--- a/extraction/petsmart.xlsx
+++ b/extraction/petsmart.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,10 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="MM/DD/YYYY"/>
-    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -69,10 +68,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,24 +443,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
@@ -590,7 +589,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Unnamed stockholders and interested parties</t>
+          <t>Some stockholders and interested parties (unnamed)</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -605,8 +604,8 @@
       <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
@@ -615,7 +614,7 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>After weak Q1 results (05/21/2014), some stockholders and interested parties urged strategic or financial alternatives, including a levered return of capital and a sale of the Company.</t>
+          <t>After the 05/21/2014 earnings miss, some stockholders and interested parties suggested alternatives, including a levered return of capital and a sale. Longview also met the board in May without advocating a transaction. Count: unknown.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -625,13 +624,13 @@
       </c>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
-      <c r="T2" s="3" t="n">
+      <c r="T2" s="4" t="n">
+        <v>41800</v>
+      </c>
+      <c r="U2" s="4" t="n">
         <v>41780</v>
       </c>
-      <c r="U2" s="3" t="n">
-        <v>41780</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" s="4" t="n">
         <v>41820</v>
       </c>
     </row>
@@ -646,7 +645,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Wachtell Lipton</t>
+          <t>Wachtell, Lipton, Rosen &amp; Katz</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -661,8 +660,8 @@
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
@@ -671,7 +670,7 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Target legal adviser; first seen acting at 06/18 board meeting, which chose to focus on capital return and formed ad hoc committee (Josefowicz, Gangwal, Stemberg).</t>
+          <t>Target legal adviser; first seen acting at the 06/18/2014 board meeting, which formed an ad hoc committee (Josefowicz, Gangwal, Stemberg) and focused on returning capital rather than a sale.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -681,13 +680,13 @@
       </c>
       <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
-      <c r="T3" s="3" t="n">
+      <c r="T3" s="4" t="n">
         <v>41808</v>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="U3" s="4" t="n">
         <v>41808</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" s="4" t="n">
         <v>41808</v>
       </c>
     </row>
@@ -702,7 +701,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Unnamed financial advisor</t>
+          <t>Unnamed financial advisor (target)</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
@@ -717,8 +716,8 @@
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
@@ -727,7 +726,7 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Unnamed financial advisor to the board, first seen acting 06/18; board then authorized vetting and retention of a financial advisor. Not mentioned again.</t>
+          <t>Target financial adviser, unnamed, first seen acting at the 06/18/2014 meeting. The board then authorized vetting and retention of a financial adviser (J.P. Morgan hired in July, #6). The filing does not say whether this adviser continued.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -737,13 +736,13 @@
       </c>
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
-      <c r="T4" s="3" t="n">
+      <c r="T4" s="4" t="n">
         <v>41808</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="4" t="n">
         <v>41808</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="4" t="n">
         <v>41808</v>
       </c>
     </row>
@@ -773,8 +772,8 @@
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
@@ -783,23 +782,23 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13D at 9.9%; sought review of alternatives including a sale. Further 13D amendments and public letters in July–August advocating a sale; met the Company 07/10/2014 advocating a sale.</t>
+          <t>Schedule 13D disclosing a 9.9% stake and a plan to press for a review including a sale. JANA advocated a sale in person on 07/10/2014 and in public letters and 13D amendments through July–August.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>“JANA Partners filed a Schedule 13D with the SEC disclosing that JANA had acquired 9.9% of the Company’s outstanding common stock” (p. 22)</t>
+          <t>“JANA intended to engage in discussions with management and the board with respect to a review of strategic alternatives, including a sale of the Company” (p. 22)</t>
         </is>
       </c>
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
-      <c r="T5" s="3" t="n">
+      <c r="T5" s="4" t="n">
         <v>41823</v>
       </c>
-      <c r="U5" s="3" t="n">
+      <c r="U5" s="4" t="n">
         <v>41823</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="4" t="n">
         <v>41823</v>
       </c>
     </row>
@@ -814,7 +813,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Longview</t>
+          <t>Longview Asset Management</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -829,8 +828,8 @@
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
@@ -839,7 +838,7 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Shareholder; public letter urging board to consider a sale; would consider rolling some or all holdings into buyer equity. Met board in May without advocating; reiterated sale advocacy 07/10/2014.</t>
+          <t>Public letter urging the board to consider a sale; Longview offered to consider rolling part or all of its holdings into the acquirer’s equity if necessary. It reiterated its advocacy of a sale on 07/10/2014. Longview managed about 9% of the stock (p. 29).</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -849,13 +848,13 @@
       </c>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
-      <c r="T6" s="3" t="n">
+      <c r="T6" s="4" t="n">
         <v>41827</v>
       </c>
-      <c r="U6" s="3" t="n">
+      <c r="U6" s="4" t="n">
         <v>41827</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="4" t="n">
         <v>41827</v>
       </c>
     </row>
@@ -885,8 +884,8 @@
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
@@ -895,7 +894,7 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Target’s sole financial adviser, retained after interviews; engagement letter effective 08/21/2014; fee up to about $39 million; gave fairness opinion 12/13/2014.</t>
+          <t>Target’s financial adviser (the only named bank, so primary), retained in July after interviews; engagement letter effective 08/21/2014 (p. 30). Fee up to about $39 million. Rendered the fairness opinion on 12/13/2014, confirmed in writing 12/14/2014.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -905,13 +904,13 @@
       </c>
       <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
-      <c r="T7" s="3" t="n">
+      <c r="T7" s="4" t="n">
         <v>41836</v>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="U7" s="4" t="n">
         <v>41821</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="4" t="n">
         <v>41851</v>
       </c>
     </row>
@@ -945,8 +944,8 @@
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
@@ -957,27 +956,27 @@
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Privately-held industry competitor; contacted J.P. Morgan after rumours, may revisit spring 2014 talks (PetSmart-initiated merger/acquisition discussions, which IP rebuffed citing antitrust). No price.</t>
+          <t>First contact in this sale context: a privately held industry competitor approached J.P. Morgan with no price, having heard rumours of a mandate. The target’s spring 2014 merger/acquisition talks with it are not recorded as a sale process (see Deal facts).</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“Industry Participant might be interested in re-visiting the conversations that had taken place in the Spring concerning the feasibility of a possible combination of the two Companies” (p. 22)</t>
+          <t>“if the Company were to pursue strategic alternatives, Industry Participant might be interested in re-visiting the conversations that had taken place in the Spring” (p. 22)</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S8" s="2" t="n"/>
-      <c r="T8" s="3" t="n">
+      <c r="T8" s="4" t="n">
         <v>41858</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U8" s="4" t="n">
         <v>41858</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="4" t="n">
         <v>41858</v>
       </c>
     </row>
@@ -992,7 +991,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PetSmart board</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="D9" s="2" t="n"/>
@@ -1007,8 +1006,8 @@
       <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
@@ -1017,7 +1016,7 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Board decided to explore alternatives incl. a sale, with Profit Improvement Plan as standalone fallback; ad hoc committee to oversee; J.P. Morgan outreach deferred to late Sept/early Oct; public announcement planned.</t>
+          <t>Board decided to explore strategic alternatives, including a sale, and to test sale value. It also ordered a Profit Improvement Plan for either path. The ad hoc committee oversees the process; J.P. Morgan to contact parties in late September/early October; public announcement planned.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1027,13 +1026,13 @@
       </c>
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
-      <c r="T9" s="3" t="n">
+      <c r="T9" s="4" t="n">
         <v>41864</v>
       </c>
-      <c r="U9" s="3" t="n">
+      <c r="U9" s="4" t="n">
         <v>41864</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="4" t="n">
         <v>41864</v>
       </c>
     </row>
@@ -1043,22 +1042,18 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>mid-August – 10/03/2014</t>
+          <t>08/19/2014</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>24 financial participants</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Sale process announced</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -1067,40 +1062,34 @@
       <c r="G10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n">
-        <v>24</v>
-      </c>
+      <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Parties contacted J.P. Morgan (inbound); includes potential lead buyers and large equity suppliers. All 27 reported to board by 10/03. Reasons section: Company “contacted or were contacted by more than 25”.</t>
+          <t>Press release issued with Q2 earnings announcing the exploration of alternatives, including a possible sale, so that parties not contacted could approach J.P. Morgan.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>“J.P. Morgan was contacted by 27 potential participants in a sale process, including three strategic parties (not counting Industry Participant) and 24 financial participants” (p. 23)</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“the Company issued a press release announcing that it determined to explore strategic alternatives for the Company to maximize value for stockholders, including a possible sale of the Company” (p. 23)</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
-      <c r="T10" s="3" t="n">
-        <v>41864</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>41864</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>41915</v>
+      <c r="T10" s="4" t="n">
+        <v>41870</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>41870</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>41870</v>
       </c>
     </row>
     <row r="11">
@@ -1109,12 +1098,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>mid-August – 10/03/2014</t>
+          <t>08/27/2014</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3 strategic parties</t>
+          <t>Industry Participant</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1124,7 +1113,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1133,36 +1122,40 @@
       <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Inbound contacts to J.P. Morgan, excluding Industry Participant. None signed a confidentiality agreement (all 15 signers were financial).</t>
+          <t>Target refuses admission: on committee direction, J.P. Morgan told Industry Participant of the board’s antitrust and information concerns (08/22) and said it would not be invited, though a proposal would be considered. The board reaffirmed this on 10/03/2014. No contact since; it never entered.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“J.P. Morgan was contacted by 27 potential participants in a sale process, including three strategic parties (not counting Industry Participant) and 24 financial participants” (p. 23)</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="n"/>
+          <t>“The J.P. Morgan representative stated that Industry Participant would not be invited into the exploratory process” (p. 23)</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S11" s="2" t="n"/>
-      <c r="T11" s="3" t="n">
-        <v>41864</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>41864</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>41915</v>
+      <c r="T11" s="4" t="n">
+        <v>41878</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>41878</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>41878</v>
       </c>
     </row>
     <row r="12">
@@ -1171,18 +1164,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>08/19/2014</t>
+          <t>mid-August–October 2014 (by 10/03/2014)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n"/>
+          <t>3 strategic parties</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sale process announced</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -1191,34 +1188,40 @@
       <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
+      <c r="M12" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Press release with Q2 earnings; intended to let parties not contacted approach J.P. Morgan on their own initiative.</t>
+          <t>Inbound: these parties contacted J.P. Morgan (Industry Participant excluded). All 27 contacts were reported to the board on 10/03/2014, which bounds the date. None later signed an NDA (all 15 signers were financial). Rows 11–12 reconcile to 27.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>“the Company issued a press release announcing that it determined to explore strategic alternatives for the Company to maximize value for stockholders, including a possible sale of the Company” (p. 23)</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="n"/>
+          <t>“J.P. Morgan was contacted by 27 potential participants in a sale process, including three strategic parties (not counting Industry Participant) and 24 financial participants” (p. 23)</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S12" s="2" t="n"/>
-      <c r="T12" s="3" t="n">
-        <v>41870</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>41870</v>
-      </c>
-      <c r="V12" s="3" t="n">
-        <v>41870</v>
+      <c r="T12" s="4" t="n">
+        <v>41889</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>41864</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>41915</v>
       </c>
     </row>
     <row r="13">
@@ -1227,22 +1230,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>08/27/2014</t>
+          <t>mid-August–October 2014 (by 10/03/2014)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Industry Participant</t>
+          <t>24 financial participants</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -1251,40 +1254,40 @@
       <c r="G13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Target refused admission: on ad hoc committee direction, J.P. Morgan conveyed concerns (08/22), then said IP not invited (antitrust, information, delay risks); proposals would be considered. Reaffirmed 10/03. No later contact; never entered.</t>
+          <t>Inbound contacts to J.P. Morgan, including potential lead buyers and large equity suppliers to lead buyers. The board heard on 10/03/2014 that about 15 parties were interested. Assumption: the 15 NDA signers (#14) are among these 24.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>“The J.P. Morgan representative stated that Industry Participant would not be invited into the exploratory process” (p. 23)</t>
+          <t>“J.P. Morgan was contacted by 27 potential participants in a sale process, including three strategic parties (not counting Industry Participant) and 24 financial participants” (p. 23)</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S13" s="2" t="n"/>
-      <c r="T13" s="3" t="n">
-        <v>41878</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>41878</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>41878</v>
+      <c r="T13" s="4" t="n">
+        <v>41889</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>41864</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>41915</v>
       </c>
     </row>
     <row r="14">
@@ -1298,7 +1301,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PetSmart / J.P. Morgan</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
@@ -1313,8 +1316,8 @@
       <c r="G14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
@@ -1323,7 +1326,7 @@
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Round 1 opened by the NDA wave (buyers came to target; no outreach wave reported). Board told 10/03 about 15 parties interested.</t>
+          <t>Round 1 opened by the NDA wave (#14): buyers came to J.P. Morgan and no target outreach is reported. Signers got diligence, senior-management presentations and detailed plan information, including on the Profit Improvement Plan, during October. IOIs due 10/30 (#15).</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1337,13 +1340,13 @@
         </is>
       </c>
       <c r="S14" s="2" t="n"/>
-      <c r="T14" s="3" t="n">
+      <c r="T14" s="4" t="n">
         <v>41916</v>
       </c>
-      <c r="U14" s="3" t="n">
+      <c r="U14" s="4" t="n">
         <v>41913</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="4" t="n">
         <v>41919</v>
       </c>
     </row>
@@ -1377,8 +1380,8 @@
       <c r="G15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
@@ -1389,7 +1392,7 @@
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Confidentiality and standstill agreements. All 15 did diligence in October, had senior-management presentations and detailed business-plan and Profit Improvement Plan information. Includes Buyer Group, Bidder 2 and all IOI submitters.</t>
+          <t>Confidentiality and standstill agreements; these barred a topping bid after signing (p. 28). Includes the Buyer Group, Bidder 2 and the later Bidder 3 members. All 15 received the same diligence access (see #13). The 15 counts parties (“financial buyers”).</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -1397,15 +1400,19 @@
           <t>“In the first week of October 2014, the Company entered into confidentiality and standstill agreements with 15 potentially interested financial buyers” (p. 23)</t>
         </is>
       </c>
-      <c r="R15" s="2" t="n"/>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S15" s="2" t="n"/>
-      <c r="T15" s="3" t="n">
+      <c r="T15" s="4" t="n">
         <v>41916</v>
       </c>
-      <c r="U15" s="3" t="n">
+      <c r="U15" s="4" t="n">
         <v>41913</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="4" t="n">
         <v>41919</v>
       </c>
     </row>
@@ -1415,12 +1422,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>during October 2014</t>
+          <t>October 2014</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>PetSmart / J.P. Morgan</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -1435,8 +1442,8 @@
       <c r="G16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
@@ -1445,7 +1452,7 @@
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Non-binding preliminary IOIs due 10/30. Bidders told Longview would roll over up to 7.5 million shares if bidder wished; asked to indicate interest, not a condition.</t>
+          <t>Non-binding preliminary indications of interest due 10/30/2014. The day of communication is not reported, only that it was in October.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -1453,16 +1460,20 @@
           <t>“During October, the potential bidders were informed that non-binding preliminary indications of interest would be due on October 30, 2014.” (p. 23)</t>
         </is>
       </c>
-      <c r="R16" s="2" t="n"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="n"/>
-      <c r="T16" s="3" t="n">
+      <c r="T16" s="4" t="n">
         <v>41927</v>
       </c>
-      <c r="U16" s="3" t="n">
+      <c r="U16" s="4" t="n">
         <v>41913</v>
       </c>
-      <c r="V16" s="3" t="n">
-        <v>41941</v>
+      <c r="V16" s="4" t="n">
+        <v>41942</v>
       </c>
     </row>
     <row r="17">
@@ -1471,22 +1482,18 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>10/30/2014</t>
+          <t>October 2014</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Longview Asset Management</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1495,51 +1502,33 @@
       <c r="G17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Preliminary non-binding IOI; range. Consortium led by BC Partners funds (later with CDPQ, GIC, StepStone). Terms beyond price not reported.</t>
+          <t>Rollover permitted: the target told bidders that Longview would roll over up to 7.5 million shares if a bidder wished. Bidders were to state interest in their IOIs; this was not a condition of participation.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>“including the Buyer Group, which indicated a range of $81.00 to $83.00 per share” (p. 24)</t>
+          <t>“Longview had informed the Company that it would be willing to “roll-over” up to 7.5 million shares on terms and price acceptable to Longview” (p. 23)</t>
         </is>
       </c>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
-      <c r="T17" s="3" t="n">
-        <v>41942</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>41942</v>
-      </c>
-      <c r="V17" s="3" t="n">
+      <c r="T17" s="4" t="n">
+        <v>41927</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>41913</v>
+      </c>
+      <c r="V17" s="4" t="n">
         <v>41942</v>
       </c>
     </row>
@@ -1554,7 +1543,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Unnamed financial bidder 1</t>
+          <t>Buyer Group (BC Partners-led consortium)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1573,11 +1562,11 @@
       <c r="G18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>85</v>
+      <c r="H18" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>83</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1601,27 +1590,23 @@
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Preliminary non-binding IOI; range. Advanced 11/03; on recommended reading, later part of Bidder 3.</t>
+          <t>Diligence open per narrative: further extensive diligence and management presentations continued in November (p. 24). Non-binding preliminary IOI; one of three first IOIs reaching at least $80.00. Consortium: BC Partners, La Caisse, GIC, StepStone (p. 1).</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“and another bidder, which suggested a range of $80.00 to $85.00 per share” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“the Buyer Group, which indicated a range of $81.00 to $83.00 per share” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
-      <c r="T18" s="3" t="n">
+      <c r="T18" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="U18" s="3" t="n">
+      <c r="U18" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="4" t="n">
         <v>41942</v>
       </c>
     </row>
@@ -1636,7 +1621,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Unnamed financial bidder 2</t>
+          <t>Unnamed bidder A</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1655,8 +1640,12 @@
       <c r="G19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
+      <c r="H19" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>85</v>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -1679,27 +1668,27 @@
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Third of three IOIs whose range “reached at least $80.00”; endpoints not disclosed, so price cells blank. Advanced 11/03; on recommended reading, later part of Bidder 3.</t>
+          <t>Diligence open per narrative: further diligence in November (p. 24). Non-binding preliminary IOI. Advanced 11/03; inferred member of Bidder 3 (#29).</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“Three bidders initially indicated price ranges that reached at least $80.00 per share” (p. 24)</t>
+          <t>“another bidder, which suggested a range of $80.00 to $85.00 per share” (p. 24)</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S19" s="2" t="n"/>
-      <c r="T19" s="3" t="n">
+      <c r="T19" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="U19" s="3" t="n">
+      <c r="U19" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="4" t="n">
         <v>41942</v>
       </c>
     </row>
@@ -1714,7 +1703,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2</t>
+          <t>Unnamed bidder B</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1733,12 +1722,8 @@
       <c r="G20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>78</v>
-      </c>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -1761,23 +1746,27 @@
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Preliminary non-binding IOI at a point price.</t>
+          <t>Diligence open per narrative: further diligence in November (p. 24). Non-binding IOI; the third of three first ranges reaching at least $80.00. Its endpoints are not given, so price cells are blank. Advanced 11/03; inferred member of Bidder 3 (#29).</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“another bidder (which we refer to as “Bidder 2”), which had initially indicated a price of $78.00” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="n"/>
+          <t>“Three bidders initially indicated price ranges that reached at least $80.00 per share” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="n"/>
-      <c r="T20" s="3" t="n">
+      <c r="T20" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="U20" s="3" t="n">
+      <c r="U20" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="4" t="n">
         <v>41942</v>
       </c>
     </row>
@@ -1792,7 +1781,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2 other IOI submitters</t>
+          <t>Bidder 2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1811,8 +1800,12 @@
       <c r="G21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
+      <c r="H21" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>78</v>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -1829,33 +1822,29 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Six IOIs in total; the remaining two, prices undisclosed but below the $80.00 cut-off (inferred from the board’s advancement rule). Reasons section says IOIs came from 5 bidder groups.</t>
+          <t>Diligence open per narrative: further diligence in November (p. 24). Non-binding preliminary IOI at a point price, below the $80.00 level later used to advance bidders; revised in #24.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>“On October 30, six of the potentially interested parties submitted indications of interest.” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>“another bidder (which we refer to as “Bidder 2”), which had initially indicated a price of $78.00” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
-      <c r="T21" s="3" t="n">
+      <c r="T21" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="U21" s="3" t="n">
+      <c r="U21" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="4" t="n">
         <v>41942</v>
       </c>
     </row>
@@ -1870,13 +1859,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n"/>
+          <t>2 other IOI submitters</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1885,22 +1878,36 @@
       <c r="G22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Due date for non-binding preliminary indications of interest.</t>
+          <t>Diligence open per narrative: further diligence in November (p. 24). Residual of six submitters minus four named above (6 − 4 = 2). Prices not disclosed; implied below $80.00 by the 11/03 cut. Reasons section says 5 bidder groups (p. 27).</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>“non-binding preliminary indications of interest would be due on October 30, 2014” (p. 23)</t>
+          <t>“On October 30, six of the potentially interested parties submitted indications of interest.” (p. 24)</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -1909,13 +1916,13 @@
         </is>
       </c>
       <c r="S22" s="2" t="n"/>
-      <c r="T22" s="3" t="n">
+      <c r="T22" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="U22" s="3" t="n">
+      <c r="U22" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="4" t="n">
         <v>41942</v>
       </c>
     </row>
@@ -1925,22 +1932,18 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>by 10/30/2014</t>
+          <t>10/30/2014</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9 NDA signers without IOI</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1949,45 +1952,37 @@
       <c r="G23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15 signers − 6 submitters = 9. J.P. Morgan heard their rationales for not submitting (10/30–11/02); rationales not disclosed. Would be 10 if only 5 IOIs (Q4).</t>
+          <t>IOI due date reached; six IOIs received on the day. Bidder 2 raised its IOI during the 10/30–11/02 follow-up calls (#24).</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“including those that did not submit an indication of interest, to hear the parties’ respective rationales” (p. 24)</t>
+          <t>“non-binding preliminary indications of interest would be due on October 30, 2014” (p. 23)</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S23" s="2" t="n"/>
-      <c r="T23" s="3" t="n">
+      <c r="T23" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="U23" s="2" t="n"/>
-      <c r="V23" s="3" t="n">
+      <c r="U23" s="4" t="n">
+        <v>41942</v>
+      </c>
+      <c r="V23" s="4" t="n">
         <v>41942</v>
       </c>
     </row>
@@ -1997,12 +1992,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>10/30–11/02/2014</t>
+          <t>10/30/2014</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2</t>
+          <t>9 NDA signers that did not submit</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2012,7 +2007,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -2021,40 +2016,28 @@
       <c r="G24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Revises #19 after J.P. Morgan calls on rationales for price levels; raised $78.00 to a range, bringing it above the $80.00 cut-off.</t>
+          <t>15 signers − 6 submitters = 9. J.P. Morgan heard their reasons for not bidding (10/30–11/02) but the reasons are not disclosed. Never mentioned again. If the Reasons figure of 5 groups is right, the count is 10.</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>“which had initially indicated a price of $78.00, increased its indication to a range of $81.00 to $84.00 per share” (p. 24)</t>
+          <t>“representatives of J.P. Morgan spoke by telephone with all of the potentially interested parties, including those that did not submit an indication of interest” (p. 24)</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -2063,14 +2046,14 @@
         </is>
       </c>
       <c r="S24" s="2" t="n"/>
-      <c r="T24" s="3" t="n">
-        <v>41943</v>
-      </c>
-      <c r="U24" s="3" t="n">
+      <c r="T24" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="V24" s="3" t="n">
-        <v>41945</v>
+      <c r="U24" s="4" t="n">
+        <v>41942</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>41942</v>
       </c>
     </row>
     <row r="25">
@@ -2079,58 +2062,80 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>11/03/2014</t>
+          <t>10/30/2014–11/02/2014</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>PetSmart board</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n"/>
+          <t>Bidder 2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="n"/>
-      <c r="M25" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Board advanced four bidders at or above $80.00 (Buyer Group, Bidder 2, Unnamed financial bidders 1 and 2) to the “final round”; November diligence, management presentations, updated FY2014 projections for all.</t>
+          <t>Diligence open per narrative: further diligence in November (p. 24). Raised from $78.00 (#20) after follow-up calls with J.P. Morgan. Still a preliminary indication.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“determined to allow the four bidders that had indicated a price or range at or above $80.00 per share to proceed to the final round of the sale process” (p. 24)</t>
+          <t>“which had initially indicated a price of $78.00, increased its indication to a range of $81.00 to $84.00 per share” (p. 24)</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S25" s="2" t="n"/>
-      <c r="T25" s="3" t="n">
-        <v>41946</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>41946</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>41946</v>
+      <c r="T25" s="4" t="n">
+        <v>41943</v>
+      </c>
+      <c r="U25" s="4" t="n">
+        <v>41942</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>41945</v>
       </c>
     </row>
     <row r="26">
@@ -2144,7 +2149,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2 other IOI submitters</t>
+          <t>2 eliminated IOI submitters</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2163,8 +2168,8 @@
       <c r="G26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
@@ -2179,27 +2184,27 @@
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Below board’s $80.00 cut-off; notified after the meeting. None indicated interest or ability to go above its initial indication.</t>
+          <t>Board advanced only bidders at or above $80.00; these two (#21) were below it. When notified, none would go above its initial indication. Exit decided by target.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>“representatives of J.P. Morgan notified the eliminated parties, none of which indicated any interest or ability to remain in the process at price levels above their respective initial indications.” (p. 24)</t>
+          <t>“representatives of J.P. Morgan notified the eliminated parties, none of which indicated any interest or ability to remain in the process” (p. 24)</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q2; Q4</t>
         </is>
       </c>
       <c r="S26" s="2" t="n"/>
-      <c r="T26" s="3" t="n">
+      <c r="T26" s="4" t="n">
         <v>41946</v>
       </c>
-      <c r="U26" s="3" t="n">
+      <c r="U26" s="4" t="n">
         <v>41946</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="4" t="n">
         <v>41946</v>
       </c>
     </row>
@@ -2209,18 +2214,18 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>November 2014 (by 12/04/2014)</t>
+          <t>11/03/2014</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>PetSmart board</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -2229,8 +2234,8 @@
       <c r="G27" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
@@ -2239,24 +2244,28 @@
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Final bids initially due Friday 12/05/2014, with completion targeted 12/15. In November form merger agreement circulated with instruction to submit comments together with final bids.</t>
+          <t>Board advanced four bidders (Buyer Group, Bidder 2, bidders A and B) to the “final round”. November: further diligence and management presentations; form merger agreement circulated, with comments due with final bids. All finalists indicated interest in a Longview rollover but did not condition on it.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>“had initially set Friday, December 5 as the date for submission of bids” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="n"/>
+          <t>“determined to allow the four bidders that had indicated a price or range at or above $80.00 per share to proceed to the final round” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q4</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="n"/>
-      <c r="T27" s="3" t="n">
-        <v>41961</v>
-      </c>
-      <c r="U27" s="3" t="n">
+      <c r="T27" s="4" t="n">
         <v>41946</v>
       </c>
-      <c r="V27" s="3" t="n">
-        <v>41977</v>
+      <c r="U27" s="4" t="n">
+        <v>41946</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>41946</v>
       </c>
     </row>
     <row r="28">
@@ -2265,12 +2274,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>November 2014 (after 11/03)</t>
+          <t>November 2014</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Bidder 3 (Unnamed financial bidders 1 and 2)</t>
+          <t>Finalists (Buyer Group, Bidder 2, bidders A/B)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2280,7 +2289,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Bidding group changed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2289,44 +2298,34 @@
       <c r="G28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Ad hoc committee let two bidders work together: one (final-round invitee) wanted an equity partner given deal size; other would drop out otherwise. Members inferred as bidders 1 and 2. Count = net reduction.</t>
+          <t>Projections revised after bidding began: after Q3 earnings, J.P. Morgan gave the bidders updated FY2014 projections at their request. Extrapolated FY2020–24 forecasts and downside sensitivities were not given to the Buyer Group, or in the sensitivities’ case to any party (pp. 37–39).</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“the ad hoc committee authorized these two bidders to work together. We refer to these two bidders together as “Bidder 3.”” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“representatives of J.P. Morgan provided the bidders with updates to the Company’s fiscal year 2014 financial projections” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n"/>
-      <c r="T28" s="3" t="n">
-        <v>41964</v>
-      </c>
-      <c r="U28" s="3" t="n">
+      <c r="T28" s="4" t="n">
+        <v>41959</v>
+      </c>
+      <c r="U28" s="4" t="n">
         <v>41946</v>
       </c>
-      <c r="V28" s="3" t="n">
-        <v>41983</v>
+      <c r="V28" s="4" t="n">
+        <v>41973</v>
       </c>
     </row>
     <row r="29">
@@ -2335,18 +2334,18 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/04–12/05/2014</t>
+          <t>by 12/03/2014</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>PetSmart (ad hoc committee)</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Deadline revised</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2355,8 +2354,8 @@
       <c r="G29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
@@ -2365,28 +2364,28 @@
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Final-bid due date moved from 12/05 to evening of 12/10 to shorten post-bid period and leak risk; bidders asked to send markups and financing commitments in advance.</t>
+          <t>Bid due date initially set for Friday 12/05/2014, with completion targeted for 12/15 to allow further rounds, final documentation and time to negotiate a Longview rollover. The day it was set is not reported.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“Accordingly, the Company set the evening of Wednesday, December 10 (five days, rather than 10 days prior to the anticipated December 15 completion date)” (p. 25)</t>
+          <t>“had initially set Friday, December 5 as the date for submission of bids” (p. 24)</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S29" s="2" t="n"/>
-      <c r="T29" s="3" t="n">
-        <v>41977</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>41977</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>41978</v>
+      <c r="T29" s="4" t="n">
+        <v>41961</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>41946</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>41976</v>
       </c>
     </row>
     <row r="30">
@@ -2395,12 +2394,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>12/10/2014</t>
+          <t>November 2014 (after 11/03/2014)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group</t>
+          <t>Bidder 3 (Unnamed bidders A + B)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2410,7 +2409,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Bidding group changed</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -2419,51 +2418,43 @@
       <c r="G30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="4" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Final bid letter with revised merger agreement and transaction documents. Financing commitment documents supplied 12/06. Documents less conditional than Bidder 2’s. Not dependent on Longview rollover.</t>
+          <t>Committee let two finalists bid jointly (one wanted an equity partner; the other would otherwise drop out). Inference: they are bidders A and B, the only finalists other than the Buyer Group and Bidder 2. Change: 2 independent units become 1 joint bidder; live units 4 → 3.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“The Buyer Group offered $80.70 per share, in cash, and Bidder 2 offered $80.35 per share, in cash.” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="n"/>
+          <t>“the ad hoc committee authorized these two bidders to work together. We refer to these two bidders together as “Bidder 3.”” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="n"/>
-      <c r="T30" s="3" t="n">
-        <v>41983</v>
-      </c>
-      <c r="U30" s="3" t="n">
-        <v>41983</v>
-      </c>
-      <c r="V30" s="3" t="n">
+      <c r="T30" s="4" t="n">
+        <v>41964</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>41946</v>
+      </c>
+      <c r="V30" s="4" t="n">
         <v>41983</v>
       </c>
     </row>
@@ -2473,22 +2464,18 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>12/10/2014</t>
+          <t>12/04/2014–12/05/2014</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline revised</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2497,52 +2484,38 @@
       <c r="G31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="4" t="n">
-        <v>80.34999999999999</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>80.34999999999999</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Final bid letter with revised merger agreement and transaction documents; documents more conditional than Buyer Group’s; financing status not reported until 12/12. Would partner with Longview only after signing.</t>
+          <t>Ad hoc committee moved the final-bid due date from 12/05 to the evening of 12/10, keeping 12/15 as completion, to reduce leak risk. Bidders were also asked to send merger-agreement markups and financing commitments in advance where possible.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“The Buyer Group offered $80.70 per share, in cash, and Bidder 2 offered $80.35 per share, in cash.” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="n"/>
+          <t>“the Company set the evening of Wednesday, December 10 (five days, rather than 10 days prior to the anticipated December 15 completion date) as the deadline” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S31" s="2" t="n"/>
-      <c r="T31" s="3" t="n">
-        <v>41983</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>41983</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>41983</v>
+      <c r="T31" s="4" t="n">
+        <v>41977</v>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>41977</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>41978</v>
       </c>
     </row>
     <row r="32">
@@ -2556,13 +2529,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n"/>
+          <t>Buyer Group (BC Partners-led consortium)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2571,37 +2548,51 @@
       <c r="G32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
+      <c r="H32" s="3" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Final-bid due date (evening). Two written bids received; Bidder 3 gave only a verbal valuation.</t>
+          <t>Financing commitment documents delivered 12/06; no diligence condition reported. Final bid letter with revised merger agreement; its documents were less conditional and more acceptable to the Company than Bidder 2’s. Not dependent on a Longview rollover.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“PetSmart received final bid letters along with revised versions of the merger agreement and other transaction documents from the Buyer Group and from Bidder 2” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>“The Buyer Group offered $80.70 per share, in cash, and Bidder 2 offered $80.35 per share, in cash.” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
-      <c r="T32" s="3" t="n">
+      <c r="T32" s="4" t="n">
         <v>41983</v>
       </c>
-      <c r="U32" s="3" t="n">
+      <c r="U32" s="4" t="n">
         <v>41983</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="4" t="n">
         <v>41983</v>
       </c>
     </row>
@@ -2616,7 +2607,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Bidder 3</t>
+          <t>Bidder 2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2626,7 +2617,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2635,43 +2626,51 @@
       <c r="G33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
+      <c r="H33" s="3" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>Value at or below market price</t>
-        </is>
-      </c>
+      <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Verbal valuation not above the ~$78 stock price; J.P. Morgan said it was unlikely to be competitive, so no written offer. Both sides contributed. Not mentioned again.</t>
+          <t>Financing status not reported for this bid; its documents were more conditional than the Buyer Group’s. Final bid letter with revised merger agreement. Not dependent on a rollover; would partner with Longview only after signing.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“Bidder 3 verbally communicated to J.P. Morgan that their valuation would not be above the current stock price of approximately $78 per share.” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
+          <t>“The Buyer Group offered $80.70 per share, in cash, and Bidder 2 offered $80.35 per share, in cash.” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n"/>
-      <c r="T33" s="3" t="n">
+      <c r="T33" s="4" t="n">
         <v>41983</v>
       </c>
-      <c r="U33" s="3" t="n">
+      <c r="U33" s="4" t="n">
         <v>41983</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="4" t="n">
         <v>41983</v>
       </c>
     </row>
@@ -2686,13 +2685,13 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>PetSmart (ad hoc committee)</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Deadline revised</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2701,8 +2700,8 @@
       <c r="G34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
@@ -2711,27 +2710,27 @@
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Neither bid acceptable unless improved: J.P. Morgan told both bidders to raise their bids, improved bids due 12/12. Treated as an extension within the final round, not a new round.</t>
+          <t>Final-bid due date reached; written bids came from the Buyer Group and Bidder 2, and Bidder 3 gave only an oral valuation (#34).</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“inform each bidder that it would need to increase its bid, and to instruct the bidders to submit improved bids on December 12, 2014.” (p. 25)</t>
+          <t>“On December 10, PetSmart received final bid letters along with revised versions of the merger agreement and other transaction documents from the Buyer Group and from Bidder 2” (p. 25)</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q2</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S34" s="2" t="n"/>
-      <c r="T34" s="3" t="n">
+      <c r="T34" s="4" t="n">
         <v>41983</v>
       </c>
-      <c r="U34" s="3" t="n">
+      <c r="U34" s="4" t="n">
         <v>41983</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="4" t="n">
         <v>41983</v>
       </c>
     </row>
@@ -2741,12 +2740,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>12/12/2014 (early)</t>
+          <t>12/10/2014</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group / Longview</t>
+          <t>Bidder 3 (Unnamed bidders A + B)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2756,7 +2755,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -2765,36 +2764,44 @@
       <c r="G35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="2" t="n"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Value at or below market price</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Rollover permitted: committee approved Buyer Group’s request to work with Longview; confidentiality agreement shared bid price. Bidder 2 would consider rollover only post-signing. Both bidders met Longview 12/09 without disclosing prices.</t>
+          <t>Bidder 3 said its valuation would not exceed the roughly $78 stock price, which is not an offer. J.P. Morgan said it was unlikely to be competitive, so no written offer was made. Both sides contributed; it was not asked to improve.</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>“Early in the day on December 12, 2014, the Buyer Group requested permission to work more closely with Longview in order to include a rollover” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="n"/>
+          <t>“Bidder 3 verbally communicated to J.P. Morgan that their valuation would not be above the current stock price of approximately $78 per share.” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Q4; Q6</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="n"/>
-      <c r="T35" s="3" t="n">
-        <v>41985</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>41985</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>41985</v>
+      <c r="T35" s="4" t="n">
+        <v>41983</v>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>41983</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>41983</v>
       </c>
     </row>
     <row r="36">
@@ -2803,22 +2810,18 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>12/12/2014 (evening)</t>
+          <t>12/10/2014</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline revised</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -2827,52 +2830,38 @@
       <c r="G36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="4" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Revises #30. Confirmed to J.P. Morgan as best and final; with revised merger agreement drafts and financing commitment documents.</t>
+          <t>Committee found neither bid acceptable unless improved and not the bidders’ best, so improved bids were requested from the Buyer Group and Bidder 2 by 12/12. On 12/11, J.P. Morgan confirmed Longview was still willing to roll over.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“Representatives of J.P. Morgan confirmed via a conversation with Bidder 2 on the evening of December 12, 2014 that $81.50 per share was its best and final offer.” (p. 26)</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="n"/>
+          <t>“instructed J.P. Morgan to inform each bidder that it would need to increase its bid, and to instruct the bidders to submit improved bids on December 12, 2014” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q5</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="n"/>
-      <c r="T36" s="3" t="n">
-        <v>41985</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>41985</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>41985</v>
+      <c r="T36" s="4" t="n">
+        <v>41983</v>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>41983</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>41983</v>
       </c>
     </row>
     <row r="37">
@@ -2881,12 +2870,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>12/12/2014 (evening)</t>
+          <t>12/12/2014</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group</t>
+          <t>Buyer Group (BC Partners-led consortium)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2896,7 +2885,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -2905,27 +2894,11 @@
       <c r="G37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H37" s="4" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n">
         <v>1</v>
       </c>
@@ -2933,23 +2906,27 @@
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Revises #29. Oral offer; said it was working to raise it within hours. Financing commitments already provided.</t>
+          <t>Rollover support formed: committee approved the Buyer Group working with Longview (supporter, not a group member). They signed a confidentiality agreement sharing bid price. Longview met the Buyer Group and Bidder 2 on 12/09 without prices. Bidder 2 would consider a rollover only after signing.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“The Buyer Group initially submitted an oral offer of $82.50 per share, in cash, but stated that it was working to increase the offer within the next few hours.” (p. 26)</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="n"/>
+          <t>“Early in the day on December 12, 2014, the Buyer Group requested permission to work more closely with Longview in order to include a rollover” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="n"/>
-      <c r="T37" s="3" t="n">
+      <c r="T37" s="4" t="n">
         <v>41985</v>
       </c>
-      <c r="U37" s="3" t="n">
+      <c r="U37" s="4" t="n">
         <v>41985</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="4" t="n">
         <v>41985</v>
       </c>
     </row>
@@ -2959,12 +2936,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>12/12/2014 (later evening)</t>
+          <t>12/12/2014</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group</t>
+          <t>Bidder 2</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2983,11 +2960,11 @@
       <c r="G38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>83</v>
+      <c r="H38" s="3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>81.5</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3011,23 +2988,27 @@
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Revises #36. Best and final; revised drafts “with few exceptions” in executable form, plus financing commitments. Longview’s $250 million rollover support helped reach $83.00; members unwilling or unable to go higher.</t>
+          <t>Financing commitment documents submitted with the bid, plus a revised merger agreement. J.P. Morgan confirmed the same evening that this was Bidder 2’s best and final offer.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“Later in the evening, the Buyer Group submitted a best and final offer of $83.00 per share, in cash.” (p. 26)</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="n"/>
+          <t>“During the evening of December 12, 2014, Bidder 2 submitted an offer of $81.50 per share, in cash.” (p. 26)</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="n"/>
-      <c r="T38" s="3" t="n">
+      <c r="T38" s="4" t="n">
         <v>41985</v>
       </c>
-      <c r="U38" s="3" t="n">
+      <c r="U38" s="4" t="n">
         <v>41985</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="4" t="n">
         <v>41985</v>
       </c>
     </row>
@@ -3042,13 +3023,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n"/>
+          <t>Buyer Group (BC Partners-led consortium)</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -3057,37 +3042,55 @@
       <c r="G39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
+      <c r="H39" s="3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Due date for improved bids; both remaining bidders submitted that evening.</t>
+          <t>Financing commitment documents in hand since 12/06. Oral interim offer, which the Buyer Group said it was working to raise within hours; superseded by #39.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“During the evening of December 12, 2014, Bidder 2 submitted an offer of $81.50 per share, in cash.” (p. 26)</t>
+          <t>“The Buyer Group initially submitted an oral offer of $82.50 per share, in cash, but stated that it was working to increase the offer within the next few hours.” (p. 26)</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1; Q7</t>
         </is>
       </c>
       <c r="S39" s="2" t="n"/>
-      <c r="T39" s="3" t="n">
+      <c r="T39" s="4" t="n">
         <v>41985</v>
       </c>
-      <c r="U39" s="3" t="n">
+      <c r="U39" s="4" t="n">
         <v>41985</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="4" t="n">
         <v>41985</v>
       </c>
     </row>
@@ -3097,12 +3100,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>12/13/2014</t>
+          <t>12/12/2014</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group</t>
+          <t>Buyer Group (BC Partners-led consortium)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3112,7 +3115,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -3121,11 +3124,27 @@
       <c r="G40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
+      <c r="H40" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="n">
         <v>1</v>
       </c>
@@ -3133,24 +3152,28 @@
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Board selected Buyer Group: approved merger at $83.00 cash, subject to resolving remaining open points in the agreement; J.P. Morgan gave fairness opinion.</t>
+          <t>Financing commitment documents submitted; revised agreements “with few exceptions, in substantially executable form”. Best and final. The Buyer Group said some members could not go higher and that Longview’s $250 million rollover helped it reach $83.00 (p. 27).</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“The board’s determination was subject, however, to confirmation that the remaining open points in the merger agreement had been satisfactorily resolved” (p. 26)</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="n"/>
+          <t>“Later in the evening, the Buyer Group submitted a best and final offer of $83.00 per share, in cash.” (p. 26)</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="n"/>
-      <c r="T40" s="3" t="n">
-        <v>41986</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>41986</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>41986</v>
+      <c r="T40" s="4" t="n">
+        <v>41985</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>41985</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>41985</v>
       </c>
     </row>
     <row r="41">
@@ -3159,18 +3182,18 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>12/14/2014</t>
+          <t>12/12/2014</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -3179,36 +3202,38 @@
       <c r="G41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n"/>
       <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Parent’s counsel: named as copy recipient for notices to Parent in the merger agreement. Role inferred; first seen at signing.</t>
+          <t>Improved-bid due date reached; both remaining bidders submitted on the evening of 12/12. The board reviewed the bids on 12/13 and approved the Buyer Group deal subject to resolving open points.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“with a copy to: Simpson Thacher and Bartlett LLP” (p. A-46)</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="n"/>
+          <t>“In addition, each bidder submitted a revised draft of the merger agreement and other transaction agreements, and copies of their respective financing commitment documents.” (p. 26)</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q5</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="n"/>
-      <c r="T41" s="3" t="n">
-        <v>41987</v>
-      </c>
-      <c r="U41" s="2" t="n"/>
-      <c r="V41" s="3" t="n">
-        <v>41987</v>
+      <c r="T41" s="4" t="n">
+        <v>41985</v>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>41985</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>41985</v>
       </c>
     </row>
     <row r="42">
@@ -3222,7 +3247,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group</t>
+          <t>Buyer Group (Argos Holdings Inc.)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3241,8 +3266,8 @@
       <c r="G42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
@@ -3253,23 +3278,27 @@
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>$83.00 per share in cash. Parent Argos Holdings (BC Partners-affiliated). Equity up to $1.83bn plus Longview rollover (3,012,050 shares, $250m); debt up to $6.95bn (Citi-led); Longview voting agreement. No go-shop.</t>
+          <t>Agreed $83.00 per share in cash. The board approved on 12/13 after J.P. Morgan’s fairness opinion. Longview signed a voting agreement (7.5%) and a rollover agreement (3,012,050 shares, about $250 million). Committed debt and equity financing (pp. 40–41). No go-shop.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“On December 14, 2014, the parties executed the merger agreement, the voting agreement and related transaction agreements” (p. 26)</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="n"/>
+          <t>“On December 14, 2014, the parties executed the merger agreement, the voting agreement and related transaction agreements and issued a press release announcing the transaction.” (p. 26)</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S42" s="2" t="n"/>
-      <c r="T42" s="3" t="n">
+      <c r="T42" s="4" t="n">
         <v>41987</v>
       </c>
-      <c r="U42" s="3" t="n">
+      <c r="U42" s="4" t="n">
         <v>41987</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="4" t="n">
         <v>41987</v>
       </c>
     </row>
@@ -3303,8 +3332,8 @@
       <c r="G43" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
@@ -3319,23 +3348,27 @@
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Best and final $81.50 below Buyer Group’s $83.00.</t>
+          <t>Still in with a best and final $81.50 (#37) when the target signed with the Buyer Group at $83.00. Exit decided by target.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>“neither of which was willing to make a definitive offer at a price above $81.50, which was lower than the $83.00 price offered by the Buyer Group” (p. 27)</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="n"/>
+          <t>“ultimately negotiated with the Buyer Group as well as two other bidding groups, neither of which was willing to make a definitive offer at a price above $81.50” (p. 27)</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S43" s="2" t="n"/>
-      <c r="T43" s="3" t="n">
+      <c r="T43" s="4" t="n">
         <v>41987</v>
       </c>
-      <c r="U43" s="3" t="n">
+      <c r="U43" s="4" t="n">
         <v>41987</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="4" t="n">
         <v>41987</v>
       </c>
     </row>
@@ -3362,13 +3395,11 @@
       <c r="F44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
+      <c r="G44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
@@ -3377,7 +3408,7 @@
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Press release announcing the transaction on the signing date.</t>
+          <t>Press release announcing the signed merger. No unsolicited proposal had been received by the filing date, 02/02/2015 (p. 28).</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -3385,15 +3416,19 @@
           <t>“On December 14, 2014, the parties executed the merger agreement, the voting agreement and related transaction agreements and issued a press release announcing the transaction.” (p. 26)</t>
         </is>
       </c>
-      <c r="R44" s="2" t="n"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S44" s="2" t="n"/>
-      <c r="T44" s="3" t="n">
+      <c r="T44" s="4" t="n">
         <v>41987</v>
       </c>
-      <c r="U44" s="3" t="n">
+      <c r="U44" s="4" t="n">
         <v>41987</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="4" t="n">
         <v>41987</v>
       </c>
     </row>
@@ -3415,12 +3450,12 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -3483,17 +3518,17 @@
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>41916</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Confidentiality and standstill agreements signed with 15 financial buyers in first week of October (#13–14); buyers had come to J.P. Morgan, no outreach wave reported</t>
+          <t>15 financial buyers signed NDAs (first week of October); IOIs requested</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>15 financial, 0 strategic: Buyer Group, Bidder 2, Unnamed financial bidders 1 and 2, 11 other unnamed financial NDA signers</t>
+          <t>15 Financial: unnamed NDA signers, including the Buyer Group, Bidder 2 and Unnamed bidders A and B</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3513,12 +3548,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>6 bidders (non-binding IOIs): Buyer Group $81–83, Unnamed financial bidder 1 $80–85, Unnamed financial bidder 2 (range reaching ≥$80), Bidder 2 $78 then $81–84, 2 others below $80</t>
+          <t>6: Buyer Group, Bidder 2, Unnamed bidder A, Unnamed bidder B, 2 unnamed</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>four advanced (≥$80.00), two eliminated 11/03, nine did not submit</t>
+          <t>four advanced (Buyer Group, Bidder 2, A, B), two eliminated, nine did not submit</t>
         </is>
       </c>
     </row>
@@ -3529,22 +3564,22 @@
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>41946</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Board advanced the four bidders at or above $80.00 to the “final round” (#24); bidders told to send merger-agreement comments with final bids</t>
+          <t>board advanced four bidders at or above $80 to the “final round”</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>4 financial: Buyer Group, Bidder 2, Unnamed financial bidders 1 and 2 (the latter two combined as Bidder 3 in November, leaving 3 bidding units)</t>
+          <t>4 Financial: Buyer Group, Bidder 2, Unnamed bidder A, Unnamed bidder B (A and B combined as Bidder 3 in November: 3 units)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2014 → 12/10/2014 → 12/12/2014</t>
+          <t>12/05/2014 (superseded before arrival) → 12/10/2014 → 12/12/2014</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -3559,12 +3594,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2 bidders: Buyer Group ($80.70 on 12/10; $82.50 then $83.00 on 12/12), Bidder 2 ($80.35 on 12/10; $81.50 on 12/12). Bidder 3 gave only a verbal valuation ≤ ~$78</t>
+          <t>2: Buyer Group, Bidder 2 (Bidder 3 gave an oral valuation only)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Bidder 3 did not submit 12/10; Buyer Group selected 12/13; signing 12/14; Bidder 2 not selected</t>
+          <t>signing with Buyer Group at $83.00; Bidder 2 not selected; Bidder 3 did not submit</t>
         </is>
       </c>
     </row>
@@ -3580,15 +3615,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3637,27 +3672,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: one process, round 0 to early October, round 1 = preliminary indications, round 2 = final round incl. the 12/12 improved bids?</t>
+          <t>Is this one process with two rounds: round 1 for IOIs and round 2 as the final round through signing?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yes. Round 1 opens with the first-week-of-October NDA wave; round 2 opens 11/03 and is announced as final; the 12/10 demand for improved bids is a deadline extension within round 2.</t>
+          <t>Yes. Process 1. Round 1 opens with the first-week-of-October NDA wave (#13). Round 2 opens 11/03 when four bidders advance to the “final round” (#26). The 12/10 request for improved bids is a Deadline revised inside round 2 (#35). No supported alternative process boundary.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Filing says J.P. Morgan “was contacted by” 27 parties; no outreach wave reported (p. 23). Board calls the 11/03 stage the “final round” and bidders were to submit “final bids” (p. 24–25).</t>
+          <t>Buyers approached J.P. Morgan and no outreach is reported (p. 23), so the NDA wave opens round 1. Round 2 is announced as final (“final round”, p. 24; “final bids”, p. 25). C7: (a) no earlier sale attempt. The spring 2014 Industry Participant talks were about PetSmart merging with or buying that company, which was “not for sale” (p. 21). (b) No-contact gaps of two months or more: none. The late May–June 2014 contacts (end uncertain, about 06/30/2014) to 08/07/2014 are about 5–6 weeks; contacts are continuous from 08/07/2014 to signing. (c) Moot. Result: one process.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#9, #13, #24, #33–#42</t>
+          <t>#7, #10, #13, #26, #35, #36, #37, #38, #39, #40, #41, #42, #43</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>If the 12/10 request opens a round 3 (best and final), #33 becomes Round opened and #34–#42 move to round 3; the 12/10 due date becomes Enforced. If round 1 is dated from the mid-August contacts, #9–#12 move to round 1.</t>
+          <t>Alternative round map: the 12/10 request opens round 3. That moves #35–#43 to round 3, adds a Round opened row, and makes 12/10 Enforced. Recording the spring Industry Participant talks as round-0 Target interest would add one row; no process change.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -3670,27 +3705,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Deadline outcomes: 10/30 Enforced; 12/05 superseded before arrival; 12/10 Extended; 12/12 Enforced?</t>
+          <t>Do the rows reconcile to the stated populations: 27 contacts, 15 NDA signers and 6 IOIs?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Yes. The board acted on 11/03 on bids in hand; 12/10 was followed by a request for improved bids by 12/12; the board selected the Buyer Group on 12/13 on the 12/12 bids.</t>
+          <t>Yes, as recorded. Contacts: 3 + 24 = 27 (#11–#12). 15 NDA signers (#14), assumed all among the 24 financial contacts. IOIs: 4 named + 2 residual = 6 (#17–#21). Leaves 9 non-submitters (#23) and 2 eliminated (#25).</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2 raised $78.00 to $81–84 in calls from 10/30 to 11/02, which qualified it for the final round (p. 24). 12/05 due date replaced on 12/04–12/05 (p. 24–25); improved bids requested 12/10 (p. 25).</t>
+          <t>The Background gives 27 contacts, “approximately 15” interested, 15 NDA signers and six IOIs (pp. 23–24). The Reasons section says “more than 25” contacts and IOIs “from 5 bidder groups” (p. 27). Prefer the detailed Background; “5 bidder groups” may count a consortium once.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#21, #23, #28, #31, #33, #38</t>
+          <t>#11, #12, #14, #21, #23, #25</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>If Bidder 2’s revision is treated as arriving after 10/30, round 1 outcome becomes “Late bids accepted”. Under the three-round alternative in Q1, 12/10 outcome becomes Enforced.</t>
+          <t>With five IOIs: #21 becomes 1, #23 becomes 10, #25 becomes 1. The auction screen stays Met in either case.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -3703,27 +3738,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Who formed Bidder 3, and were both members live final-round invitees?</t>
+          <t>What is the outcome of round 1’s 10/30/2014 IOI due date?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Both members were among the four advanced on 11/03, i.e. Unnamed financial bidders 1 and 2; independent bidders fell from 4 to 3.</t>
+          <t>Enforced. The board selected four finalists on 11/03 on the indications in hand.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Only four advanced and later just three bidding units appear; Reasons say the Company negotiated with the Buyer Group and “two other bidding groups” (p. 24, 26). But p. 24 says only “one of which had been invited into the final round”.</t>
+          <t>Six IOIs arrived on 10/30 (p. 24). Bidder 2 raised its IOI to $81–84 during the 10/30–11/02 feedback calls (#24), and the 11/03 cut counted the raise. Its Date from is 10/30, so under C11 it is not a late bid.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#17, #18, #27, #32</t>
+          <t>#15, #22, #24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>If the second member had been eliminated on 11/03, it needs a Re-entered row, and one of the four advanced bidders has an unreported exit (inferred Not selected/Dropped); live counts in round 2 change.</t>
+          <t>If Bidder 2’s raise is treated as a late bid, the outcome becomes Late bids accepted (deadline not enforced), and Bidder 2 advanced only on its late revision.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -3736,27 +3771,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>How many preliminary indications were received: six or five?</t>
+          <t>Is Bidder 3 the joint unit of Unnamed bidders A and B, both advanced on 11/03?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Six, as narrated in the Background; 9 NDA signers did not submit.</t>
+          <t>Yes. Four bidders advanced; the final round had three units (Buyer Group, Bidder 2, Bidder 3). So Bidder 3’s members are the two finalists other than the Buyer Group and Bidder 2. #29 records the change from 4 to 3 live units.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Background: “six of the potentially interested parties submitted indications of interest” (p. 24). Reasons: indications “from 5 bidder groups” (p. 26), possibly counting Bidder 3’s two members as one group.</t>
+          <t>p. 24 says one member “had been invited into the final round” and the other “would drop out of the process” if it could not team up, which leaves its invitation implicit. p. 27 confirms the Buyer Group negotiated with “two other bidding groups”.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#20, #22, #25</t>
+          <t>#18, #19, #25, #26, #29, #34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>If five, the cohort of other submitters (#20, #25) falls to 1 and the non-submitter cohort (#22) rises to 10.</t>
+          <t>If the second member was an eliminated submitter, it needs a Re-entered row and #25 falls to 1. One of A/B would then be unaccounted for and need its own exit, and the live count in round 2 changes.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -3769,27 +3804,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Who ended Bidder 3’s participation on 12/10?</t>
+          <t>Round 2 deadline outcomes: is 12/05 superseded before arrival, 12/10 Extended and 12/12 Enforced?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Did not submit, reason Value at or below market price: it gave only a verbal valuation not above ~$78 and submitted no written offer.</t>
+          <t>Yes: 12/05 superseded before arrival (no outcome); 12/10 Extended; 12/12 Enforced.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Bidder 3’s valuation would not exceed the ~$78 stock price; J.P. Morgan said it was unlikely to be competitive “and accordingly Bidder 3 did not submit a written offer” (p. 25).</t>
+          <t>The ad hoc committee replaced 12/05 with 12/10 on 12/04–12/05 (pp. 24–25). On 12/10 it asked the same bidders for improved bids by 12/12 (p. 25), a same-round extension under C11. Both bids arrived on the evening of 12/12, and the board acted on them on 12/13 (p. 26).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#32</t>
+          <t>#28, #30, #33, #35, #40</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Could be Withdrew (bidder’s own valuation) or Dropped by target (J.P. Morgan discouraged it). The live count is the same; only who decided changes.</t>
+          <t>If the revision came on 12/05 after that date was reached, 12/05 gets a Deadline row and the outcome Extended. If 12/10 opens a round 3, 12/10 becomes Enforced.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -3802,33 +3837,66 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Should Industry Participant count as an entered participant?</t>
+          <t>Is Bidder 3’s 12/10 statement a bid, and who ended its participation?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>No. It expressed interest without a price, signed no confidentiality agreement and was refused admission, so it gets no exit row.</t>
+          <t>It is not a bid. Did not submit, with Exit reason “Value at or below market price”. Both sides contributed.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>IP “would not be invited into the exploratory process”; no contact after 08/27/2014 (p. 23). Spring 2014 talks were PetSmart-initiated merger/acquisition talks, not a sale approach (p. 21).</t>
+          <t>Bidder 3 gave only an oral valuation ceiling at the roughly $78 stock price. J.P. Morgan said it was unlikely to be competitive, and “accordingly Bidder 3 did not submit a written offer” (p. 25). C12 treats a valuation without an offer as no bid.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#7, #12</t>
+          <t>#34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>If treated as a round-0 bidder, #12 becomes Dropped by target (Terms or process: antitrust risk), adding one strategic entry and exit.</t>
+          <t>Recording Withdrew or Dropped by target changes only the label. An Informal Bid row with Price high $78.00 would add a priced round-2 bid.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Is the Buyer Group’s oral $82.50 offer Formal?</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Formal.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>It answered the 12/10 request for improved bids in a round announced as final (C13 item 2). It followed the Buyer Group’s Formal 12/10 bid with markup. It was oral and interim, replaced by $83.00 within hours (p. 26).</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>#38</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>If Informal, the Buyer Group’s formal price path is $80.70 → $83.00. No count or round changes.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3839,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3864,7 +3932,7 @@
           <t>Target</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>PetSmart, Inc.</t>
         </is>
@@ -3876,9 +3944,9 @@
           <t>Acquirer</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Argos Holdings Inc. (Parent) and Argos Merger Sub Inc., affiliates of funds advised by BC Partners; owned at closing by the Buyer Group: BC Partners funds, La Caisse de dépôt et placement du Québec, GIC Special Investments affiliates, StepStone Group affiliates and, after 12/12/2014, Longview (rollover of 3,012,050 shares)</t>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Argos Holdings Inc. (Parent; merger sub Argos Merger Sub Inc.), affiliated with funds advised by BC Partners and owned at closing by the Buyer Group: BC Partners funds, La Caisse de dépôt et placement du Québec, GIC Special Investments affiliates, StepStone Group affiliates and, after 12/12/2014, Longview Asset Management as rollover holder</t>
         </is>
       </c>
     </row>
@@ -3888,9 +3956,9 @@
           <t>Acquirer type</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Financial (private-equity-led consortium; Longview rollover is support, not a separate bidder)</t>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Financial (private-equity-led consortium; Longview rollover is support, not a group member)</t>
         </is>
       </c>
     </row>
@@ -3900,9 +3968,9 @@
           <t>Agreed price and consideration</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>$83.00 per share in cash</t>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>$83.00 per share in cash; Longview rolls 3,012,050 shares (about $250 million) into Parent instead of taking cash</t>
         </is>
       </c>
     </row>
@@ -3912,8 +3980,10 @@
           <t>Merger agreement signed</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>41987</v>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>12/14/2014</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -3922,8 +3992,10 @@
           <t>Merger announced</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>41987</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>12/14/2014</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -3932,7 +4004,7 @@
           <t>Filing type and date</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>DEFM14A, 02/02/2015</t>
         </is>
@@ -3944,7 +4016,7 @@
           <t>Background pages</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>21–26</t>
         </is>
@@ -3956,7 +4028,7 @@
           <t>Initiation</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>activist-influenced</t>
         </is>
@@ -3968,84 +4040,98 @@
           <t>Number of processes</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Auction screen</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Met — 15 financial buyers signed confidentiality and standstill agreements (first week of October 2014)</t>
+          <t>Earlier approaches</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Undated, unspecified inquiries “from time to time” about the Company’s interest in a sale (p. 21). Q1 and spring 2014: target-initiated exploration of a merger with or acquisition of Industry Participant, a private competitor. It said it was not for sale and raised antitrust concerns; no agreement. This was the target acting as possible acquirer, not a sale process, so it has no rows.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Whole-company bids</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Auction screen</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Met (process 1): 15 parties. The filing counts agreements with 15 “potentially interested financial buyers”, i.e. parties. No post-signing additions, so the pre-signing subtotal is also 15. Longview’s confidentiality agreements (before 12/09 and with the Buyer Group on 12/12) are rollover-holder agreements and do not count.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Currency and units of bid prices</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>US dollars per share</t>
+          <t>Whole-company bids</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Target financial advisers</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>J.P. Morgan (sole retained financial adviser; engagement letter effective 08/21/2014); an unnamed financial advisor attended the 06/18/2014 board meeting</t>
+          <t>Currency and units of bid prices</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>US dollars per share</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Target legal advisers</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Wachtell, Lipton, Rosen &amp; Katz</t>
+          <t>Target financial advisers</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>J.P. Morgan Securities LLC (primary; retained July 2014, engagement letter effective 08/21/2014; fairness opinion); an unnamed financial advisor attended the 06/18/2014 board meeting</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Target legal advisers</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Wachtell, Lipton, Rosen &amp; Katz</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>After weak first-quarter 2014 results and public pressure from JANA Partners (9.9%) and Longview, PetSmart’s board decided on 08/13/2014 to explore a sale, announced it on 08/19, and kept the strategic Industry Participant out on antitrust grounds. J.P. Morgan was approached by 27 parties; 15 financial buyers signed confidentiality agreements in early October and six submitted non-binding indications on 10/30/2014. On 11/03 the board advanced the four at or above $80.00 per share to a final round, where two of them were allowed to combine as Bidder 3. At the 12/10 final-bid deadline the Buyer Group bid $80.70 and Bidder 2 $80.35 with agreement markups, while Bidder 3 valued PetSmart no higher than its ~$78 share price and did not submit. Told to improve by 12/12, Bidder 2 offered $81.50 best and final and the Buyer Group, helped by a Longview rollover, $83.00. The board approved the Buyer Group’s $83.00 cash offer on 12/13 and the merger agreement was signed and announced on 12/14/2014.</t>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>PetSmart’s first-quarter report missed expectations in May 2014. Activists JANA Partners and Longview then pushed for a sale, and on 08/13/2014 the board decided to explore one, announcing it on 08/19/2014. The board refused to admit Industry Participant, a strategic competitor, on antitrust and information grounds. Of 27 parties that approached J.P. Morgan, 15 financial buyers signed confidentiality and standstill agreements, and six submitted non-binding indications on 10/30/2014; four at $80 or above advanced to a final round, where two teamed up as Bidder 3. On 12/10 the Buyer Group bid $80.70 and Bidder 2 $80.35, while Bidder 3 would not exceed the roughly $78 share price. Asked to improve by 12/12, Bidder 2 gave a best-and-final $81.50, and the BC Partners-led Buyer Group, helped by a Longview rollover, went from $82.50 to $83.00 cash, signed and announced on 12/14/2014.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B17"/>
+  <autoFilter ref="A1:B18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/extraction/petsmart.xlsx
+++ b/extraction/petsmart.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -60,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -72,6 +72,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -439,14 +442,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
@@ -455,7 +458,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -584,15 +587,15 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>late May–June 2014</t>
+          <t>late May and June 2014</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Some stockholders and interested parties (unnamed)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n"/>
+          <t>Some stockholders and interested parties</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Activist</t>
@@ -606,15 +609,15 @@
       </c>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>After the 05/21/2014 earnings miss, some stockholders and interested parties suggested alternatives, including a levered return of capital and a sale. Longview also met the board in May without advocating a transaction. Count: unknown.</t>
+          <t>Count: unknown. After weak Q1 results (05/21/2014), stockholders and interested parties suggested strategic or financial alternatives, including a levered return of capital and a sale. Senders not named.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -622,13 +625,13 @@
           <t>“the Company received written or verbal communications from some stockholders and from interested parties suggesting that the Company engage in various strategic or financial alternatives” (p. 21)</t>
         </is>
       </c>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
       <c r="T2" s="4" t="n">
-        <v>41800</v>
+        <v>41799</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>41780</v>
+        <v>41779</v>
       </c>
       <c r="V2" s="4" t="n">
         <v>41820</v>
@@ -645,10 +648,10 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Wachtell, Lipton, Rosen &amp; Katz</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n"/>
+          <t>Unnamed financial advisor</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Adviser</t>
@@ -662,15 +665,15 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Target legal adviser; first seen acting at the 06/18/2014 board meeting, which formed an ad hoc committee (Josefowicz, Gangwal, Stemberg) and focused on returning capital rather than a sale.</t>
+          <t>Target financial adviser, unnamed, attended the 06/18/2014 board review of alternatives. Board then authorized vetting and retention of a financial advisor and retained J.P. Morgan (#6); filing does not say whether this advisor continued.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -678,8 +681,8 @@
           <t>“the board reviewed, together with a financial advisor and with Wachtell, Lipton, Rosen &amp; Katz (“Wachtell Lipton”), its legal advisor” (p. 21)</t>
         </is>
       </c>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="4" t="n">
         <v>41808</v>
       </c>
@@ -701,10 +704,10 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Unnamed financial advisor (target)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n"/>
+          <t>Wachtell, Lipton, Rosen &amp; Katz</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Adviser</t>
@@ -718,24 +721,24 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Target financial adviser, unnamed, first seen acting at the 06/18/2014 meeting. The board then authorized vetting and retention of a financial adviser (J.P. Morgan hired in July, #6). The filing does not say whether this adviser continued.</t>
+          <t>Target legal adviser throughout. At this meeting the board chose to explore capital-structure changes (return of capital), not a sale, and formed the ad hoc committee (Josefowicz, Gangwal, Stemberg).</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>“At a meeting on June 18, 2014, the board reviewed, together with a financial advisor and with Wachtell” (p. 21)</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2" t="n"/>
+          <t>“the board reviewed, together with a financial advisor and with Wachtell, Lipton, Rosen &amp; Katz (“Wachtell Lipton”), its legal advisor” (p. 21)</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
       <c r="T4" s="4" t="n">
         <v>41808</v>
       </c>
@@ -760,7 +763,7 @@
           <t>JANA Partners</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Activist</t>
@@ -774,24 +777,24 @@
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Schedule 13D disclosing a 9.9% stake and a plan to press for a review including a sale. JANA advocated a sale in person on 07/10/2014 and in public letters and 13D amendments through July–August.</t>
+          <t>Schedule 13D: 9.9% stake; intends to discuss strategic alternatives including a sale. Met the Company 07/10/2014 advocating a sale; further 13D amendments and public letters in July and August advocating a sale.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>“JANA intended to engage in discussions with management and the board with respect to a review of strategic alternatives, including a sale of the Company” (p. 22)</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="n"/>
-      <c r="S5" s="2" t="n"/>
+          <t>“JANA Partners filed a Schedule 13D with the SEC disclosing that JANA had acquired 9.9% of the Company’s outstanding common stock” (p. 22)</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="4" t="n">
         <v>41823</v>
       </c>
@@ -816,7 +819,7 @@
           <t>Longview Asset Management</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Activist</t>
@@ -830,15 +833,15 @@
       </c>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Public letter urging the board to consider a sale; Longview offered to consider rolling part or all of its holdings into the acquirer’s equity if necessary. It reiterated its advocacy of a sale on 07/10/2014. Longview managed about 9% of the stock (p. 29).</t>
+          <t>Public letter: board should consider a sale; Longview might roll part or all of its holdings into acquirer equity if needed. Met board in May 2014 without advocating a transaction; reiterated sale advocacy 07/10/2014.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -846,8 +849,8 @@
           <t>“Longview made public a letter to the board in which Longview stated that the board should consider the a sale of the Company” (p. 22)</t>
         </is>
       </c>
-      <c r="R6" s="2" t="n"/>
-      <c r="S6" s="2" t="n"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
       <c r="T6" s="4" t="n">
         <v>41827</v>
       </c>
@@ -869,10 +872,10 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>J.P. Morgan</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
+          <t>J.P. Morgan Securities LLC</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Adviser</t>
@@ -886,15 +889,15 @@
       </c>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Target’s financial adviser (the only named bank, so primary), retained in July after interviews; engagement letter effective 08/21/2014 (p. 30). Fee up to about $39 million. Rendered the fairness opinion on 12/13/2014, confirmed in writing 12/14/2014.</t>
+          <t>Target financial adviser, retained in July after interviews; engagement letter effective 08/21/2014 (Opinion section, p. 30). Rendered fairness opinion on $83.00 on 12/13/2014 (written 12/14/2014). Order against #4–#5 unknown.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -902,8 +905,8 @@
           <t>“In July, after interviewing several potential financial advisors, the Company retained J.P. Morgan as financial advisor” (p. 22)</t>
         </is>
       </c>
-      <c r="R7" s="2" t="n"/>
-      <c r="S7" s="2" t="n"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
       <c r="T7" s="4" t="n">
         <v>41836</v>
       </c>
@@ -946,30 +949,26 @@
       </c>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>First contact in this sale context: a privately held industry competitor approached J.P. Morgan with no price, having heard rumours of a mandate. The target’s spring 2014 merger/acquisition talks with it are not recorded as a sale process (see Deal facts).</t>
+          <t>First contact in the sale process, inbound to J.P. Morgan, no price. Privately held industry competitor with controlling stockholders. Spring 2014 talks were PetSmart-initiated; Industry Participant then said it was not for sale and raised antitrust concerns.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“if the Company were to pursue strategic alternatives, Industry Participant might be interested in re-visiting the conversations that had taken place in the Spring” (p. 22)</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="n"/>
+          <t>“Industry Participant might be interested in re-visiting the conversations that had taken place in the Spring concerning the feasibility of a possible combination” (p. 22)</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
       <c r="T8" s="4" t="n">
         <v>41858</v>
       </c>
@@ -994,7 +993,7 @@
           <t>PetSmart</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Target sale decision</t>
@@ -1008,24 +1007,24 @@
       </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Board decided to explore strategic alternatives, including a sale, and to test sale value. It also ordered a Profit Improvement Plan for either path. The ad hoc committee oversees the process; J.P. Morgan to contact parties in late September/early October; public announcement planned.</t>
+          <t>Board decided to explore alternatives including a sale; Profit Improvement Plan for sale or standalone; ad hoc committee to oversee. Planned J.P. Morgan outreach for late September/early October and a public announcement; weighed antitrust and information risks of inviting Industry Participant.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“the board (1) determined to explore strategic alternatives (including a possible sale of the Company) for the Company to maximize value for stockholders” (p. 22)</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n"/>
-      <c r="S9" s="2" t="n"/>
+          <t>“determined to explore strategic alternatives (including a possible sale of the Company) for the Company to maximize value for stockholders” (p. 22)</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
       <c r="T9" s="4" t="n">
         <v>41864</v>
       </c>
@@ -1050,7 +1049,7 @@
           <t>PetSmart</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Sale process announced</t>
@@ -1060,19 +1059,19 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Press release issued with Q2 earnings announcing the exploration of alternatives, including a possible sale, so that parties not contacted could approach J.P. Morgan.</t>
+          <t>Press release with Q2 earnings: exploring strategic alternatives including a possible sale. Board intended it to let uncontacted interested parties approach J.P. Morgan.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1080,8 +1079,8 @@
           <t>“the Company issued a press release announcing that it determined to explore strategic alternatives for the Company to maximize value for stockholders, including a possible sale of the Company” (p. 23)</t>
         </is>
       </c>
-      <c r="R10" s="2" t="n"/>
-      <c r="S10" s="2" t="n"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
       <c r="T10" s="4" t="n">
         <v>41870</v>
       </c>
@@ -1098,48 +1097,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>08/27/2014</t>
+          <t>08/19/2014</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Industry Participant</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Target refuses admission: on committee direction, J.P. Morgan told Industry Participant of the board’s antitrust and information concerns (08/22) and said it would not be invited, though a proposal would be considered. The board reaffirmed this on 10/03/2014. No contact since; it never entered.</t>
+          <t>Round 1 (indications of interest) opens with the public announcement (#9), the direct execution of the 08/13 decision and the first solicitation of buyers; inbound contacts followed (#12–#13). Planned outbound outreach is not separately reported.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“The J.P. Morgan representative stated that Industry Participant would not be invited into the exploratory process” (p. 23)</t>
+          <t>“would ensure that interested parties not contacted would become aware of the process and could contact J.P. Morgan on their own initiative” (p. 22)</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1147,15 +1140,15 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="S11" s="2" t="n"/>
+      <c r="S11" s="2" t="inlineStr"/>
       <c r="T11" s="4" t="n">
-        <v>41878</v>
+        <v>41870</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>41878</v>
+        <v>41870</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>41878</v>
+        <v>41870</v>
       </c>
     </row>
     <row r="12">
@@ -1164,12 +1157,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>mid-August–October 2014 (by 10/03/2014)</t>
+          <t>08/27/2014</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3 strategic parties</t>
+          <t>Industry Participant</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1179,49 +1172,49 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Inbound: these parties contacted J.P. Morgan (Industry Participant excluded). All 27 contacts were reported to the board on 10/03/2014, which bounds the date. None later signed an NDA (all 15 signers were financial). Rows 11–12 reconcile to 27.</t>
+          <t>Target refuses admission: ad hoc committee had J.P. Morgan convey board concerns (call 08/22); on 08/27 Industry Participant said it would discuss a combination and was told it would not be invited, though a proposal would be considered. No contact since; board reaffirmed 10/03/2014.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>“J.P. Morgan was contacted by 27 potential participants in a sale process, including three strategic parties (not counting Industry Participant) and 24 financial participants” (p. 23)</t>
+          <t>“The J.P. Morgan representative stated that Industry Participant would not be invited into the exploratory process” (p. 23)</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="n"/>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr"/>
       <c r="T12" s="4" t="n">
-        <v>41889</v>
+        <v>41878</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>41864</v>
+        <v>41878</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>41915</v>
+        <v>41878</v>
       </c>
     </row>
     <row r="13">
@@ -1230,12 +1223,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>mid-August–October 2014 (by 10/03/2014)</t>
+          <t>mid-August to end of October 2014</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24 financial participants</t>
+          <t>24 financial parties</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1252,21 +1245,21 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Inbound contacts to J.P. Morgan, including potential lead buyers and large equity suppliers to lead buyers. The board heard on 10/03/2014 that about 15 parties were interested. Assumption: the 15 NDA signers (#14) are among these 24.</t>
+          <t>Inbound: parties contacted J.P. Morgan. Includes potential lead buyers and large equity suppliers to lead buyers. Filing total 27 (with #13), excluding Industry Participant. Fifteen financial buyers signed NDAs (#14); overlap not stated but implied.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1276,18 +1269,18 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="n"/>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr"/>
       <c r="T13" s="4" t="n">
-        <v>41889</v>
+        <v>41902</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>41864</v>
+        <v>41862</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>41915</v>
+        <v>41943</v>
       </c>
     </row>
     <row r="14">
@@ -1296,18 +1289,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>first week of October 2014</t>
+          <t>mid-August to end of October 2014</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n"/>
+          <t>3 strategic parties</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1318,20 +1315,22 @@
       </c>
       <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Round 1 opened by the NDA wave (#14): buyers came to J.P. Morgan and no target outreach is reported. Signers got diligence, senior-management presentations and detailed plan information, including on the Profit Improvement Plan, during October. IOIs due 10/30 (#15).</t>
+          <t>Inbound: contacted J.P. Morgan; excludes Industry Participant. No strategic party signed an NDA (all 15 signers financial, #14), so none entered.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>“In the first week of October 2014, the Company entered into confidentiality and standstill agreements with 15 potentially interested financial buyers” (p. 23)</t>
+          <t>“J.P. Morgan was contacted by 27 potential participants in a sale process, including three strategic parties (not counting Industry Participant) and 24 financial participants” (p. 23)</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -1339,15 +1338,15 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="S14" s="2" t="n"/>
+      <c r="S14" s="2" t="inlineStr"/>
       <c r="T14" s="4" t="n">
-        <v>41916</v>
+        <v>41902</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>41913</v>
+        <v>41862</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>41919</v>
+        <v>41943</v>
       </c>
     </row>
     <row r="15">
@@ -1382,30 +1381,30 @@
       </c>
       <c r="H15" s="3" t="n"/>
       <c r="I15" s="3" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Confidentiality and standstill agreements; these barred a topping bid after signing (p. 28). Includes the Buyer Group, Bidder 2 and the later Bidder 3 members. All 15 received the same diligence access (see #13). The 15 counts parties (“financial buyers”).</t>
+          <t>Confidentiality and standstill agreements (standstills barred topping bids after signing, p. 28). All 15 did October diligence, got senior management presentations and detailed plan data incl. Profit Improvement Plan. Board told 10/03 approximately 15 parties interested.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>“In the first week of October 2014, the Company entered into confidentiality and standstill agreements with 15 potentially interested financial buyers” (p. 23)</t>
+          <t>“the Company entered into confidentiality and standstill agreements with 15 potentially interested financial buyers” (p. 23)</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="n"/>
+          <t>Q2; Q3</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr"/>
       <c r="T15" s="4" t="n">
         <v>41916</v>
       </c>
@@ -1430,7 +1429,7 @@
           <t>PetSmart</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Deadline set</t>
@@ -1444,28 +1443,24 @@
       </c>
       <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Non-binding preliminary indications of interest due 10/30/2014. The day of communication is not reported, only that it was in October.</t>
+          <t>Non-binding preliminary indications due 10/30/2014. Bidders told Longview would roll over up to 7.5 million shares on terms acceptable to it, if the bidder wished; asked to state interest in Longview, not a condition of participation.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“During October, the potential bidders were informed that non-binding preliminary indications of interest would be due on October 30, 2014.” (p. 23)</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="n"/>
+          <t>“the potential bidders were informed that non-binding preliminary indications of interest would be due on October 30, 2014” (p. 23)</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="4" t="n">
         <v>41927</v>
       </c>
@@ -1482,18 +1477,18 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>October 2014</t>
+          <t>10/30/2014</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Longview Asset Management</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n"/>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1504,29 +1499,33 @@
       </c>
       <c r="H17" s="3" t="n"/>
       <c r="I17" s="3" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Rollover permitted: the target told bidders that Longview would roll over up to 7.5 million shares if a bidder wished. Bidders were to state interest in their IOIs; this was not a condition of participation.</t>
+          <t>Round 1 due date reached; six indications received (#17–#21). J.P. Morgan then called all 15 NDA signers, 10/30–11/02, about price rationales or non-submission.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>“Longview had informed the Company that it would be willing to “roll-over” up to 7.5 million shares on terms and price acceptable to Longview” (p. 23)</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="n"/>
-      <c r="S17" s="2" t="n"/>
+          <t>“On October 30, six of the potentially interested parties submitted indications of interest.” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="4" t="n">
-        <v>41927</v>
+        <v>41942</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>41913</v>
+        <v>41942</v>
       </c>
       <c r="V17" s="4" t="n">
         <v>41942</v>
@@ -1543,7 +1542,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group (BC Partners-led consortium)</t>
+          <t>Buyer Group</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1586,20 +1585,24 @@
       <c r="M18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: further extensive diligence and management presentations continued in November (p. 24). Non-binding preliminary IOI; one of three first IOIs reaching at least $80.00. Consortium: BC Partners, La Caisse, GIC, StepStone (p. 1).</t>
+          <t>Diligence still open (further diligence in November), no condition stated: Unclear. Non-binding preliminary indication; interest in Longview rollover, not a condition. Consortium composition at this date not stated.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“the Buyer Group, which indicated a range of $81.00 to $83.00 per share” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="n"/>
-      <c r="S18" s="2" t="n"/>
+          <t>“including the Buyer Group, which indicated a range of $81.00 to $83.00 per share” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="4" t="n">
         <v>41942</v>
       </c>
@@ -1621,7 +1624,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Unnamed bidder A</t>
+          <t>Unnamed financial bidder 1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1664,11 +1667,11 @@
       <c r="M19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: further diligence in November (p. 24). Non-binding preliminary IOI. Advanced 11/03; inferred member of Bidder 3 (#29).</t>
+          <t>Diligence still open, no condition stated: Unclear. Non-binding preliminary indication. One of three initial indications reaching $80; advanced 11/03 (#24). Inferred to be a Bidder 3 member (#27).</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -1678,10 +1681,10 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="n"/>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr"/>
       <c r="T19" s="4" t="n">
         <v>41942</v>
       </c>
@@ -1703,7 +1706,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Unnamed bidder B</t>
+          <t>Unnamed financial bidder 2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1742,11 +1745,11 @@
       <c r="M20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: further diligence in November (p. 24). Non-binding IOI; the third of three first ranges reaching at least $80.00. Its endpoints are not given, so price cells are blank. Advanced 11/03; inferred member of Bidder 3 (#29).</t>
+          <t>Diligence still open, no condition stated: Unclear. Third initial indication whose range reached at least $80.00; endpoints not disclosed, so price cells blank. Advanced 11/03 (#24); inferred to be a Bidder 3 member (#27).</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -1756,10 +1759,10 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="n"/>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr"/>
       <c r="T20" s="4" t="n">
         <v>41942</v>
       </c>
@@ -1824,11 +1827,11 @@
       <c r="M21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: further diligence in November (p. 24). Non-binding preliminary IOI at a point price, below the $80.00 level later used to advance bidders; revised in #24.</t>
+          <t>Diligence still open, no condition stated: Unclear. Non-binding preliminary indication at a point price of $78.00; revised by #23.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -1836,8 +1839,8 @@
           <t>“another bidder (which we refer to as “Bidder 2”), which had initially indicated a price of $78.00” (p. 24)</t>
         </is>
       </c>
-      <c r="R21" s="2" t="n"/>
-      <c r="S21" s="2" t="n"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="4" t="n">
         <v>41942</v>
       </c>
@@ -1859,7 +1862,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2 other IOI submitters</t>
+          <t>2 other indication submitters</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1898,11 +1901,11 @@
       <c r="M22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="n"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: further diligence in November (p. 24). Residual of six submitters minus four named above (6 − 4 = 2). Prices not disclosed; implied below $80.00 by the 11/03 cut. Reasons section says 5 bidder groups (p. 27).</t>
+          <t>Diligence still open, no condition stated: Unclear. 6 submitters − 4 named or described (#17–#20) = 2. Prices not disclosed; below $80.00, as they were not among the four at or above $80 (#24).</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -1915,7 +1918,7 @@
           <t>Q2</t>
         </is>
       </c>
-      <c r="S22" s="2" t="n"/>
+      <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="4" t="n">
         <v>41942</v>
       </c>
@@ -1932,18 +1935,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/30/2014</t>
+          <t>by 10/30/2014</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n"/>
+          <t>9 NDA signers without an indication</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1954,34 +1961,38 @@
       </c>
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
-      <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>IOI due date reached; six IOIs received on the day. Bidder 2 raised its IOI during the 10/30–11/02 follow-up calls (#24).</t>
+          <t>15 NDA signers (#14) − 6 submitters (#16) = 9. Filing confirms non-submitters and that J.P. Morgan heard their rationales, which are not disclosed. Not reported again.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“non-binding preliminary indications of interest would be due on October 30, 2014” (p. 23)</t>
+          <t>“including those that did not submit an indication of interest” (p. 24)</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="n"/>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="U23" s="4" t="n">
-        <v>41942</v>
-      </c>
+      <c r="U23" s="4" t="n"/>
       <c r="V23" s="4" t="n">
         <v>41942</v>
       </c>
@@ -1992,12 +2003,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>10/30/2014</t>
+          <t>10/30/2014 to 11/02/2014</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9 NDA signers that did not submit</t>
+          <t>Bidder 2</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2007,7 +2018,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -2016,44 +2027,56 @@
       <c r="G24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
+      <c r="H24" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15 signers − 6 submitters = 9. J.P. Morgan heard their reasons for not bidding (10/30–11/02) but the reasons are not disclosed. Never mentioned again. If the Reasons figure of 5 groups is right, the count is 10.</t>
+          <t>Diligence still open, no condition stated: Unclear. Revises #20 from $78.00 after J.P. Morgan calls; arrived after the 10/30 due date and was considered, qualifying Bidder 2 for the next round (#24).</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>“representatives of J.P. Morgan spoke by telephone with all of the potentially interested parties, including those that did not submit an indication of interest” (p. 24)</t>
+          <t>“As a result of its discussions with J.P. Morgan, another bidder (which we refer to as “Bidder 2”), which had initially indicated a price of $78.00, increased its indication” (p. 24)</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="n"/>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="4" t="n">
-        <v>41942</v>
+        <v>41943</v>
       </c>
       <c r="U24" s="4" t="n">
         <v>41942</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>41942</v>
+        <v>41945</v>
       </c>
     </row>
     <row r="25">
@@ -2062,80 +2085,58 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>10/30/2014–11/02/2014</t>
+          <t>11/03/2014</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: further diligence in November (p. 24). Raised from $78.00 (#20) after follow-up calls with J.P. Morgan. Still a preliminary indication.</t>
+          <t>Board advanced the four bidders at or above $80.00 (Buyer Group, Bidder 2, Unnamed financial bidders 1–2) to a “final round”. All got further diligence and management presentations in November; form merger agreement circulated with comments due with final bids.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“which had initially indicated a price of $78.00, increased its indication to a range of $81.00 to $84.00 per share” (p. 24)</t>
+          <t>“allow the four bidders that had indicated a price or range at or above $80.00 per share to proceed to the final round of the sale process” (p. 24)</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="n"/>
+          <t>Q1; Q2</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr"/>
       <c r="T25" s="4" t="n">
-        <v>41943</v>
+        <v>41946</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>41942</v>
+        <v>41946</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>41945</v>
+        <v>41946</v>
       </c>
     </row>
     <row r="26">
@@ -2149,7 +2150,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2 eliminated IOI submitters</t>
+          <t>2 other indication submitters</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2170,34 +2171,34 @@
       </c>
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="n"/>
+          <t>Would not improve earlier offer</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Board advanced only bidders at or above $80.00; these two (#21) were below it. When notified, none would go above its initial indication. Exit decided by target.</t>
+          <t>Below the $80.00 cut. On notice, none showed interest or ability to stay in above its initial indication. Count: 6 submitters − 4 advancing = 2.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>“representatives of J.P. Morgan notified the eliminated parties, none of which indicated any interest or ability to remain in the process” (p. 24)</t>
+          <t>“representatives of J.P. Morgan notified the eliminated parties, none of which indicated any interest or ability to remain in the process at price levels above their respective initial indications” (p. 24)</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>Q2; Q4</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="n"/>
+          <t>Q2; Q5</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="4" t="n">
         <v>41946</v>
       </c>
@@ -2214,7 +2215,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>11/03/2014</t>
+          <t>by 12/03/2014</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2222,10 +2223,10 @@
           <t>PetSmart</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -2236,36 +2237,36 @@
       </c>
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="n"/>
-      <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Board advanced four bidders (Buyer Group, Bidder 2, bidders A and B) to the “final round”. November: further diligence and management presentations; form merger agreement circulated, with comments due with final bids. All finalists indicated interest in a Longview rollover but did not condition on it.</t>
+          <t>Final bids initially due Friday 12/05/2014, with completion targeted for 12/15 to leave time for further bidding rounds if needed, documentation and a possible Longview rollover. Day set not reported; after the 11/03 round opening.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>“determined to allow the four bidders that had indicated a price or range at or above $80.00 per share to proceed to the final round” (p. 24)</t>
+          <t>“had initially set Friday, December 5 as the date for submission of bids” (p. 24)</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q4</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="n"/>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr"/>
       <c r="T27" s="4" t="n">
-        <v>41946</v>
+        <v>41961</v>
       </c>
       <c r="U27" s="4" t="n">
         <v>41946</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>41946</v>
+        <v>41976</v>
       </c>
     </row>
     <row r="28">
@@ -2274,12 +2275,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>November 2014</t>
+          <t>after 11/03/2014, by 12/10/2014</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Finalists (Buyer Group, Bidder 2, bidders A/B)</t>
+          <t>Bidder 3 (Unnamed financial bidders 1 and 2)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2289,7 +2290,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bidding group changed</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2300,32 +2301,42 @@
       </c>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n"/>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="n"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Projections revised after bidding began: after Q3 earnings, J.P. Morgan gave the bidders updated FY2014 projections at their request. Extrapolated FY2020–24 forecasts and downside sensitivities were not given to the Buyer Group, or in the sensitivities’ case to any party (pp. 37–39).</t>
+          <t>2 independent finalists become 1 joint bidder, “Bidder 3”, with ad hoc committee approval: one wanted an equity partner; the other would otherwise drop out. Group change reported; identifying members as #18 and #19 is inferred.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“representatives of J.P. Morgan provided the bidders with updates to the Company’s fiscal year 2014 financial projections” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="n"/>
-      <c r="S28" s="2" t="n"/>
+          <t>“the ad hoc committee authorized these two bidders to work together. We refer to these two bidders together as “Bidder 3.”” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr"/>
       <c r="T28" s="4" t="n">
-        <v>41959</v>
+        <v>41964</v>
       </c>
       <c r="U28" s="4" t="n">
         <v>41946</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>41973</v>
+        <v>41983</v>
       </c>
     </row>
     <row r="29">
@@ -2334,7 +2345,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>by 12/03/2014</t>
+          <t>after 11/03/2014, by 12/10/2014</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2342,10 +2353,10 @@
           <t>PetSmart</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2356,36 +2367,32 @@
       </c>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Bid due date initially set for Friday 12/05/2014, with completion targeted for 12/15 to allow further rounds, final documentation and time to negotiate a Longview rollover. The day it was set is not reported.</t>
+          <t>Gave updated projections to all finalists: after Q3 earnings, at bidders’ request, J.P. Morgan provided updated FY2014 projections. FY2020–2024 extrapolations were never given to the Buyer Group (Projections section, p. 37).</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“had initially set Friday, December 5 as the date for submission of bids” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="n"/>
+          <t>“representatives of J.P. Morgan provided the bidders with updates to the Company’s fiscal year 2014 financial projections” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
       <c r="T29" s="4" t="n">
-        <v>41961</v>
+        <v>41964</v>
       </c>
       <c r="U29" s="4" t="n">
         <v>41946</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>41976</v>
+        <v>41983</v>
       </c>
     </row>
     <row r="30">
@@ -2394,22 +2401,18 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>November 2014 (after 11/03/2014)</t>
+          <t>12/04/2014 to 12/05/2014</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Bidder 3 (Unnamed bidders A + B)</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Bidding group changed</t>
+          <t>Deadline revised</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -2420,42 +2423,36 @@
       </c>
       <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Committee let two finalists bid jointly (one wanted an equity partner; the other would otherwise drop out). Inference: they are bidders A and B, the only finalists other than the Buyer Group and Bidder 2. Change: 2 independent units become 1 joint bidder; live units 4 → 3.</t>
+          <t>Ad hoc committee moved final bids from 12/05 to the evening of 12/10/2014, keeping 12/15 completion to cut leak risk; asked for markups of the merger agreement and transaction documents and financing commitments in advance.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“the ad hoc committee authorized these two bidders to work together. We refer to these two bidders together as “Bidder 3.”” (p. 24)</t>
+          <t>“set the evening of Wednesday, December 10 (five days, rather than 10 days prior to the anticipated December 15 completion date) as the deadline for submission of final bids” (p. 25)</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="n"/>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr"/>
       <c r="T30" s="4" t="n">
-        <v>41964</v>
+        <v>41977</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>41946</v>
+        <v>41977</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>41983</v>
+        <v>41978</v>
       </c>
     </row>
     <row r="31">
@@ -2464,18 +2461,18 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>12/04/2014–12/05/2014</t>
+          <t>12/09/2014</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n"/>
+          <t>Longview Asset Management</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Deadline revised</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2486,36 +2483,36 @@
       </c>
       <c r="H31" s="3" t="n"/>
       <c r="I31" s="3" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Ad hoc committee moved the final-bid due date from 12/05 to the evening of 12/10, keeping 12/15 as completion, to reduce leak risk. Bidders were also asked to send merger-agreement markups and financing commitments in advance where possible.</t>
+          <t>Rollover relationship: after signing a confidentiality agreement, Longview held introductory meetings with the Buyer Group and Bidder 2 (not reported for Bidder 3). Bidders barred from disclosing intended prices. Buyer Group and Bidder 2 had sent draft comments 12/06.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“the Company set the evening of Wednesday, December 10 (five days, rather than 10 days prior to the anticipated December 15 completion date) as the deadline” (p. 25)</t>
+          <t>“J.P. Morgan arranged introductory meetings between Longview and the Buyer Group, and between Longview and Bidder 2” (p. 25)</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="n"/>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr"/>
       <c r="T31" s="4" t="n">
-        <v>41977</v>
+        <v>41982</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>41977</v>
+        <v>41982</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>41978</v>
+        <v>41982</v>
       </c>
     </row>
     <row r="32">
@@ -2529,17 +2526,13 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group (BC Partners-led consortium)</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2548,44 +2541,30 @@
       <c r="G32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H32" s="3" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Financing commitment documents delivered 12/06; no diligence condition reported. Final bid letter with revised merger agreement; its documents were less conditional and more acceptable to the Company than Bidder 2’s. Not dependent on a Longview rollover.</t>
+          <t>Round 2 final-bid due date reached: written bids from Buyer Group (#32) and Bidder 2 (#33); verbal indication only from Bidder 3 (#34).</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“The Buyer Group offered $80.70 per share, in cash, and Bidder 2 offered $80.35 per share, in cash.” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="n"/>
-      <c r="S32" s="2" t="n"/>
+          <t>“On December 10, PetSmart received final bid letters along with revised versions of the merger agreement and other transaction documents from the Buyer Group and from Bidder 2” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="4" t="n">
         <v>41983</v>
       </c>
@@ -2607,7 +2586,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2</t>
+          <t>Buyer Group</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2627,10 +2606,10 @@
         <v>2</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>80.34999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>80.34999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2644,17 +2623,17 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="n"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Financing status not reported for this bid; its documents were more conditional than the Buyer Group’s. Final bid letter with revised merger agreement. Not dependent on a rollover; would partner with Longview only after signing.</t>
+          <t>Financing commitment documents delivered 12/06, no diligence condition reported: Light. Final bid letter with revised merger agreement and transaction documents; less conditional and closer to Company positions than Bidder 2. Not dependent on Longview rollover.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -2662,8 +2641,8 @@
           <t>“The Buyer Group offered $80.70 per share, in cash, and Bidder 2 offered $80.35 per share, in cash.” (p. 25)</t>
         </is>
       </c>
-      <c r="R33" s="2" t="n"/>
-      <c r="S33" s="2" t="n"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="4" t="n">
         <v>41983</v>
       </c>
@@ -2685,13 +2664,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n"/>
+          <t>Bidder 2</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2700,30 +2683,44 @@
       <c r="G34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="n"/>
+      <c r="H34" s="3" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Final-bid due date reached; written bids came from the Buyer Group and Bidder 2, and Bidder 3 gave only an oral valuation (#34).</t>
+          <t>Financing commitment not reported until 12/12; documents more conditional than Buyer Group’s: Unclear. Final bid letter with revised merger agreement. Not dependent on Longview; partnering only after signing.</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“On December 10, PetSmart received final bid letters along with revised versions of the merger agreement and other transaction documents from the Buyer Group and from Bidder 2” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="n"/>
+          <t>“The Buyer Group offered $80.70 per share, in cash, and Bidder 2 offered $80.35 per share, in cash.” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
       <c r="T34" s="4" t="n">
         <v>41983</v>
       </c>
@@ -2745,7 +2742,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Bidder 3 (Unnamed bidders A + B)</t>
+          <t>Bidder 3</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2766,9 +2763,9 @@
       </c>
       <c r="H35" s="3" t="n"/>
       <c r="I35" s="3" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="n">
         <v>1</v>
       </c>
@@ -2777,10 +2774,10 @@
           <t>Value at or below market price</t>
         </is>
       </c>
-      <c r="O35" s="2" t="n"/>
+      <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Bidder 3 said its valuation would not exceed the roughly $78 stock price, which is not an offer. J.P. Morgan said it was unlikely to be competitive, so no written offer was made. Both sides contributed; it was not asked to improve.</t>
+          <t>Verbally said its valuation would not exceed the current stock price, about $78 (Ref: approximately $78 current price, 12/10/2014). J.P. Morgan said it was unlikely to be competitive; accordingly no written offer.</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -2790,10 +2787,10 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>Q4; Q6</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="n"/>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr"/>
       <c r="T35" s="4" t="n">
         <v>41983</v>
       </c>
@@ -2818,29 +2815,29 @@
           <t>PetSmart</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Deadline revised</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2" t="n"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Committee found neither bid acceptable unless improved and not the bidders’ best, so improved bids were requested from the Buyer Group and Bidder 2 by 12/12. On 12/11, J.P. Morgan confirmed Longview was still willing to roll over.</t>
+          <t>Ad hoc committee: no assurance the board would approve either bid unless improved; bids close and not best offers. Buyer Group and Bidder 2 told to raise bids, due 12/12/2014. J.P. Morgan confirmed Longview’s rollover willingness on 12/11.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -2850,10 +2847,10 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q5</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="n"/>
+          <t>Q1; Q6; Q8</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr"/>
       <c r="T36" s="4" t="n">
         <v>41983</v>
       </c>
@@ -2875,7 +2872,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group (BC Partners-led consortium)</t>
+          <t>Buyer Group</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2892,34 +2889,34 @@
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2" t="n"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Rollover support formed: committee approved the Buyer Group working with Longview (supporter, not a group member). They signed a confidentiality agreement sharing bid price. Longview met the Buyer Group and Bidder 2 on 12/09 without prices. Bidder 2 would consider a rollover only after signing.</t>
+          <t>Rollover support and information difference: committee let Buyer Group work with Longview; they signed a confidentiality agreement sharing bid price. Bidder 2 would accommodate Longview only after signing, with no price effect. Longview offered a voting agreement.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“Early in the day on December 12, 2014, the Buyer Group requested permission to work more closely with Longview in order to include a rollover” (p. 25)</t>
+          <t>“later that day, Longview and the Buyer Group entered into a confidentiality agreement permitting the exchange of detailed information between them, including bid price” (p. 26)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="n"/>
+          <t>Q1; Q3</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr"/>
       <c r="T37" s="4" t="n">
         <v>41985</v>
       </c>
@@ -2941,67 +2938,45 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H38" s="3" t="n"/>
+      <c r="I38" s="3" t="n"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Financing commitment documents submitted with the bid, plus a revised merger agreement. J.P. Morgan confirmed the same evening that this was Bidder 2’s best and final offer.</t>
+          <t>Round 3 due date reached; improved bids received that evening from Bidder 2 (#38) and Buyer Group (#39–#40).</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“During the evening of December 12, 2014, Bidder 2 submitted an offer of $81.50 per share, in cash.” (p. 26)</t>
+          <t>“to instruct the bidders to submit improved bids on December 12, 2014” (p. 25)</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="n"/>
+          <t>Q1; Q8</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr"/>
       <c r="T38" s="4" t="n">
         <v>41985</v>
       </c>
@@ -3023,7 +2998,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group (BC Partners-led consortium)</t>
+          <t>Bidder 2</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3040,13 +3015,13 @@
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>82.5</v>
+        <v>81.5</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>82.5</v>
+        <v>81.5</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3066,24 +3041,24 @@
       <c r="M39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Financing commitment documents in hand since 12/06. Oral interim offer, which the Buyer Group said it was working to raise within hours; superseded by #39.</t>
+          <t>Financing commitment documents submitted, no diligence condition reported: Light. Evening offer with revised merger agreement draft; J.P. Morgan confirmed it was Bidder 2’s best and final. Revises #33.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“The Buyer Group initially submitted an oral offer of $82.50 per share, in cash, but stated that it was working to increase the offer within the next few hours.” (p. 26)</t>
+          <t>“During the evening of December 12, 2014, Bidder 2 submitted an offer of $81.50 per share, in cash.” (p. 26)</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q7</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="n"/>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr"/>
       <c r="T39" s="4" t="n">
         <v>41985</v>
       </c>
@@ -3105,7 +3080,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group (BC Partners-led consortium)</t>
+          <t>Buyer Group</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3122,13 +3097,13 @@
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3148,16 +3123,16 @@
       <c r="M40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2" t="n"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Financing commitment documents submitted; revised agreements “with few exceptions, in substantially executable form”. Best and final. The Buyer Group said some members could not go higher and that Longview’s $250 million rollover helped it reach $83.00 (p. 27).</t>
+          <t>Financing commitments delivered, no diligence condition reported: Light. Oral offer, stated as being raised within hours; formal by its standing 12/10 markup and revised drafts submitted that evening. Revises #32.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“Later in the evening, the Buyer Group submitted a best and final offer of $83.00 per share, in cash.” (p. 26)</t>
+          <t>“The Buyer Group initially submitted an oral offer of $82.50 per share, in cash, but stated that it was working to increase the offer within the next few hours.” (p. 26)</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -3165,7 +3140,7 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="S40" s="2" t="n"/>
+      <c r="S40" s="2" t="inlineStr"/>
       <c r="T40" s="4" t="n">
         <v>41985</v>
       </c>
@@ -3187,45 +3162,67 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n"/>
+          <t>Buyer Group</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Improved-bid due date reached; both remaining bidders submitted on the evening of 12/12. The board reviewed the bids on 12/13 and approved the Buyer Group deal subject to resolving open points.</t>
+          <t>Financing commitment documents submitted; drafts substantially executable with few exceptions: Light. Best and final; revises #39. Group said some members could not go higher and Longview’s $250 million rollover helped reach $83.00 (p. 27).</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“In addition, each bidder submitted a revised draft of the merger agreement and other transaction agreements, and copies of their respective financing commitment documents.” (p. 26)</t>
+          <t>“Later in the evening, the Buyer Group submitted a best and final offer of $83.00 per share, in cash.” (p. 26)</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q5</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="n"/>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr"/>
       <c r="T41" s="4" t="n">
         <v>41985</v>
       </c>
@@ -3247,51 +3244,45 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group (Argos Holdings Inc.)</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Simpson Thacher and Bartlett LLP</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="n"/>
-      <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N42" s="2" t="n"/>
-      <c r="O42" s="2" t="n"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Agreed $83.00 per share in cash. The board approved on 12/13 after J.P. Morgan’s fairness opinion. Longview signed a voting agreement (7.5%) and a rollover agreement (3,012,050 shares, about $250 million). Committed debt and equity financing (pp. 40–41). No go-shop.</t>
+          <t>Buyer-side legal adviser: named as copy recipient for Parent and Merger Sub in the merger agreement notices (Annex A, Section 8.7). Its role as counsel is inferred from that listing; earliest date shown is the agreement date.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“On December 14, 2014, the parties executed the merger agreement, the voting agreement and related transaction agreements and issued a press release announcing the transaction.” (p. 26)</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="n"/>
+          <t>“Simpson Thacher and Bartlett LLP” (p. A-46)</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
       <c r="T42" s="4" t="n">
         <v>41987</v>
       </c>
@@ -3330,13 +3321,13 @@
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="n"/>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="n"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="n">
         <v>1</v>
       </c>
@@ -3345,15 +3336,15 @@
           <t>Lower offer than rivals</t>
         </is>
       </c>
-      <c r="O43" s="2" t="n"/>
+      <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Still in with a best and final $81.50 (#37) when the target signed with the Buyer Group at $83.00. Exit decided by target.</t>
+          <t>Best and final $81.50 versus Buyer Group’s $83.00; board approved the Buyer Group transaction on 12/13/2014 and the agreement was signed 12/14.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>“ultimately negotiated with the Buyer Group as well as two other bidding groups, neither of which was willing to make a definitive offer at a price above $81.50” (p. 27)</t>
+          <t>“The board noted that Bidder 2 had informed the Company’s representatives that $81.50 per share was its best and final offer.” (p. 27)</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -3361,7 +3352,7 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="S43" s="2" t="n"/>
+      <c r="S43" s="2" t="inlineStr"/>
       <c r="T43" s="4" t="n">
         <v>41987</v>
       </c>
@@ -3383,37 +3374,43 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n"/>
+          <t>Buyer Group (Argos Holdings Inc.)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Merger agreement signed</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="n"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Press release announcing the signed merger. No unsolicited proposal had been received by the filing date, 02/02/2015 (p. 28).</t>
+          <t>$83.00 cash per share. Parent owned by BC Partners funds, CDPQ, GIC, StepStone affiliates and Longview (rollover 3,012,050 shares; voting agreement 7,424,591 shares). Board approved 12/13 with J.P. Morgan opinion. Committed debt and $1.83 billion equity; no go-shop.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>“On December 14, 2014, the parties executed the merger agreement, the voting agreement and related transaction agreements and issued a press release announcing the transaction.” (p. 26)</t>
+          <t>“On December 14, 2014, the parties executed the merger agreement, the voting agreement and related transaction agreements” (p. 26)</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -3421,7 +3418,7 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="S44" s="2" t="n"/>
+      <c r="S44" s="2" t="inlineStr"/>
       <c r="T44" s="4" t="n">
         <v>41987</v>
       </c>
@@ -3432,8 +3429,66 @@
         <v>41987</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>12/14/2014</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Merger announced</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>Press release announcing the transaction issued on signing day. No unsolicited proposal received through 02/02/2015 (p. 28).</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>“issued a press release announcing the transaction” (p. 26)</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="4" t="n">
+        <v>41987</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>41987</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>41987</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V44"/>
+  <autoFilter ref="A1:V45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3444,7 +3499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3452,11 +3507,11 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3518,17 +3573,17 @@
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="n">
-        <v>41916</v>
+      <c r="C2" s="5" t="n">
+        <v>41870</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15 financial buyers signed NDAs (first week of October); IOIs requested</t>
+          <t>Public announcement of the strategic-alternatives review, inviting parties to contact J.P. Morgan (#10); NDAs first week of October (#14)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>15 Financial: unnamed NDA signers, including the Buyer Group, Bidder 2 and Unnamed bidders A and B</t>
+          <t>15 financial NDA signers, unnamed as a set; among them Buyer Group, Bidder 2, Unnamed financial bidders 1 and 2, two other indication submitters and nine non-submitters. 3 strategic contacts never signed; Industry Participant refused admission</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3538,7 +3593,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Enforced</t>
+          <t>Late bids accepted</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -3548,12 +3603,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>6: Buyer Group, Bidder 2, Unnamed bidder A, Unnamed bidder B, 2 unnamed</t>
+          <t>6: Buyer Group ($81.00–$83.00), Unnamed financial bidder 1 ($80.00–$85.00), Unnamed financial bidder 2 (range reaching at least $80), Bidder 2 ($78.00, raised to $81.00–$84.00 after the deadline), 2 others (undisclosed, below $80)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>four advanced (Buyer Group, Bidder 2, A, B), two eliminated, nine did not submit</t>
+          <t>Four advanced (at or above $80.00); two dropped by target; nine did not submit</t>
         </is>
       </c>
     </row>
@@ -3564,27 +3619,27 @@
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>41946</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>board advanced four bidders at or above $80 to the “final round”</t>
+          <t>Board selects the four bidders at or above $80.00 for the “final round” (#24)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>4 Financial: Buyer Group, Bidder 2, Unnamed bidder A, Unnamed bidder B (A and B combined as Bidder 3 in November: 3 units)</t>
+          <t>4 financial: Buyer Group, Bidder 2, Unnamed financial bidders 1 and 2 (the last two joined as Bidder 3 in November, leaving 3 units)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2014 (superseded before arrival) → 12/10/2014 → 12/12/2014</t>
+          <t>12/05/2014 (superseded before arrival) → 12/10/2014</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Extended; Enforced</t>
+          <t>Enforced</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -3594,17 +3649,63 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2: Buyer Group, Bidder 2 (Bidder 3 gave an oral valuation only)</t>
+          <t>2 written: Buyer Group $80.70, Bidder 2 $80.35 (both cash, with merger agreement markups); Bidder 3 gave only a verbal valuation not above ~$78</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>signing with Buyer Group at $83.00; Bidder 2 not selected; Bidder 3 did not submit</t>
+          <t>Two asked to improve (round 3); Bidder 3 did not submit</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>41983</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Ad hoc committee requires improved bids from Buyer Group and Bidder 2 by 12/12 (#35)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2 financial: Buyer Group, Bidder 2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12/12/2014</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Enforced</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Inferred final</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2: Bidder 2 $81.50 (best and final); Buyer Group $82.50 oral, then $83.00 best and final</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Signing with Buyer Group at $83.00 on 12/14/2014; Bidder 2 not selected</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J3"/>
+  <autoFilter ref="A1:J4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3615,16 +3716,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3672,30 +3773,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Is this one process with two rounds: round 1 for IOIs and round 2 as the final round through signing?</t>
+          <t>Is this one process with round 1 opening at the 08/19/2014 announcement, round 2 at the 11/03 final-round selection and round 3 at the 12/10 request for improved bids?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yes. Process 1. Round 1 opens with the first-week-of-October NDA wave (#13). Round 2 opens 11/03 when four bidders advance to the “final round” (#26). The 12/10 request for improved bids is a Deadline revised inside round 2 (#35). No supported alternative process boundary.</t>
+          <t>Yes: one process; round 0 holds #1–#8; three rounds as mapped.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Buyers approached J.P. Morgan and no outreach is reported (p. 23), so the NDA wave opens round 1. Round 2 is announced as final (“final round”, p. 24; “final bids”, p. 25). C7: (a) no earlier sale attempt. The spring 2014 Industry Participant talks were about PetSmart merging with or buying that company, which was “not for sale” (p. 21). (b) No-contact gaps of two months or more: none. The late May–June 2014 contacts (end uncertain, about 06/30/2014) to 08/07/2014 are about 5–6 weeks; contacts are continuous from 08/07/2014 to signing. (c) Moot. Result: one process.</t>
+          <t>The 08/19 announcement carried out the 08/13 decision and invited inbound contact (pp. 22–23); on 11/03 four were sent to the “final round” (p. 24); on 12/10 two selected bidders had to improve by 12/12 (p. 25). Gaps of two months or more without acquirer contact: none (longest about five weeks, 06/30/2014 to 08/07/2014). E5: (a) nothing to test, (b) no break, (c) no fresh start after 08/13; one process.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#7, #10, #13, #26, #35, #36, #37, #38, #39, #40, #41, #42, #43</t>
+          <t>#10–#13, #24, #35–#40, #42–#43</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Alternative round map: the 12/10 request opens round 3. That moves #35–#43 to round 3, adds a Round opened row, and makes 12/10 Enforced. Recording the spring Industry Participant talks as round-0 Target interest would add one row; no process change.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n"/>
+          <t>Alternative 1: round 1 opens with the early-October NDAs, moving #11–#13 to round 0. Alternative 2: the 12/10 request is bargaining within round 2, deleting #35, moving #36–#43 to round 2 and making the 12/10 outcome Extended.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3705,30 +3806,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Do the rows reconcile to the stated populations: 27 contacts, 15 NDA signers and 6 IOIs?</t>
+          <t>Who formed Bidder 3, and were there six first-round indications or five?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Yes, as recorded. Contacts: 3 + 24 = 27 (#11–#12). 15 NDA signers (#14), assumed all among the 24 financial contacts. IOIs: 4 named + 2 residual = 6 (#17–#21). Leaves 9 non-submitters (#23) and 2 eliminated (#25).</t>
+          <t>Bidder 3 = the other two finalists at or above $80 (Unnamed financial bidders 1 and 2); six indications, i.e. five bidder groups once Bidder 3 is counted as one.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The Background gives 27 contacts, “approximately 15” interested, 15 NDA signers and six IOIs (pp. 23–24). The Reasons section says “more than 25” contacts and IOIs “from 5 bidder groups” (p. 27). Prefer the detailed Background; “5 bidder groups” may count a consortium once.</t>
+          <t>The background reports six indications and four finalists (p. 24). One Bidder 3 member was “invited into the final round”; the other would “drop out of the process” if it could not pair up, implying it was still in (p. 24). Only three finalists acted on 12/10, and Reasons cites indications “from 5 bidder groups” and “two other bidding groups” (p. 27).</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#11, #12, #14, #21, #23, #25</t>
+          <t>#14, #18–#19, #21–#22, #24–#25, #27</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>With five IOIs: #21 becomes 1, #23 becomes 10, #25 becomes 1. The auction screen stays Met in either case.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n"/>
+          <t>If the partner had been eliminated on 11/03, a fourth finalist left without a reported exit (add an inferred exit by 12/10), #25 includes the partner and a Re-entered row is needed. If only five indications, #21 becomes Count 1 and #22 Count 10.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3738,30 +3839,30 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>What is the outcome of round 1’s 10/30/2014 IOI due date?</t>
+          <t>Were Buyer Group members separate NDA signers who later combined, and is Longview’s 12/12 link a bidding-group change?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Enforced. The board selected four finalists on 11/03 on the indications in hand.</t>
+          <t>Treat the Buyer Group as one unit throughout, and Longview as rollover support (#36), not a group change.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Six IOIs arrived on 10/30 (p. 24). Bidder 2 raised its IOI to $81–84 during the 10/30–11/02 feedback calls (#24), and the 11/03 cut counted the raise. Its Date from is 10/30, so under C11 it is not a late bid.</t>
+          <t>The filing names the Buyer Group from its 10/30 indication and never reports when it formed (p. 24); the 24 financial contacts included “large suppliers of equity capital to lead buyers” (p. 23). Longview is a shareholder rolling over shares, which E4 does not treat as a group; the definition adds Longview only after 12/12/2014 (p. 1).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#15, #22, #24</t>
+          <t>#14, #17, #30, #36</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>If Bidder 2’s raise is treated as a late bid, the outcome becomes Late bids accepted (deadline not enforced), and Bidder 2 advanced only on its late revision.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n"/>
+          <t>If members signed separately, several of the 15 signers were Buyer Group members, round 1 had fewer independent units, and a Bidding group changed row before 10/30 would be needed.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3771,30 +3872,30 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Is Bidder 3 the joint unit of Unnamed bidders A and B, both advanced on 11/03?</t>
+          <t>What was the outcome of the 10/30/2014 indication deadline?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Yes. Four bidders advanced; the final round had three units (Buyer Group, Bidder 2, Bidder 3). So Bidder 3’s members are the two finalists other than the Buyer Group and Bidder 2. #29 records the change from 4 to 3 live units.</t>
+          <t>Late bids accepted.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>p. 24 says one member “had been invited into the final round” and the other “would drop out of the process” if it could not team up, which leaves its invitation implicit. p. 27 confirms the Buyer Group negotiated with “two other bidding groups”.</t>
+          <t>Bidder 2 raised its indication from $78.00 to $81.00–$84.00 between 10/30 and 11/02 after J.P. Morgan calls, and the board admitted it on that basis on 11/03 (p. 24). Other bidders’ indications are reported only as submitted on 10/30.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#18, #19, #25, #26, #29, #34</t>
+          <t>#16, #23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>If the second member was an eliminated submitter, it needs a Re-entered row and #25 falls to 1. One of A/B would then be unaccounted for and need its own exit, and the live count in round 2 changes.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n"/>
+          <t>If the revision is read as bargaining over an on-time bid, the outcome is Enforced (board acted on bids in hand on 11/03). Participation is unaffected.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3804,30 +3905,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Round 2 deadline outcomes: is 12/05 superseded before arrival, 12/10 Extended and 12/12 Enforced?</t>
+          <t>Which exit reason fits the two indication submitters cut on 11/03?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Yes: 12/05 superseded before arrival (no outcome); 12/10 Extended; 12/12 Enforced.</t>
+          <t>Would not improve earlier offer.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>The ad hoc committee replaced 12/05 with 12/10 on 12/04–12/05 (pp. 24–25). On 12/10 it asked the same bidders for improved bids by 12/12 (p. 25), a same-round extension under C11. Both bids arrived on the evening of 12/12, and the board acted on them on 12/13 (p. 26).</t>
+          <t>They fell below the board’s $80.00 cut, and when notified none indicated any interest or ability to remain in the process above its initial indication (p. 24). That reveals a ceiling at their own bids.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#28, #30, #33, #35, #40</t>
+          <t>#25</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>If the revision came on 12/05 after that date was reached, 12/05 gets a Deadline row and the outcome Extended. If 12/10 opens a round 3, 12/10 becomes Enforced.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n"/>
+          <t>Lower offer than rivals would stress the cut against the four finalists and lose the fact that they would not raise.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3837,30 +3938,30 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Is Bidder 3’s 12/10 statement a bid, and who ended its participation?</t>
+          <t>What happened to round 2’s due dates of 12/05 and 12/10/2014?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>It is not a bid. Did not submit, with Exit reason “Value at or below market price”. Both sides contributed.</t>
+          <t>12/05 superseded before arrival (no outcome); 12/10 Enforced.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Bidder 3 gave only an oral valuation ceiling at the roughly $78 stock price. J.P. Morgan said it was unlikely to be competitive, and “accordingly Bidder 3 did not submit a written offer” (p. 25). C12 treats a valuation without an offer as no bid.</t>
+          <t>On 12/04–12/05 the committee reset final bids to the evening of 12/10 (pp. 24–25); no bids are reported on 12/05. On 12/10 the committee acted on the bids in hand, requiring improved bids from two of the three bidders; Bidder 3 was not asked (p. 25).</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#34</t>
+          <t>#26, #29, #31, #35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Recording Withdrew or Dropped by target changes only the label. An Informal Bid row with Price high $78.00 would add a priced round-2 bid.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n"/>
+          <t>If 12/05 is treated as reached before the change, add a Deadline row with outcome Extended. If round 3 merges into round 2 (Q1), the 12/10 outcome becomes Extended.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3870,33 +3971,66 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Is the Buyer Group’s oral $82.50 offer Formal?</t>
+          <t>Did Bidder 3 withdraw, fail to submit, or get dropped on 12/10?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Formal.</t>
+          <t>Did not submit; Value at or below market price.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>It answered the 12/10 request for improved bids in a round announced as final (C13 item 2). It followed the Buyer Group’s Formal 12/10 bid with markup. It was oral and interim, replaced by $83.00 within hours (p. 26).</t>
+          <t>Bidder 3 said its valuation would not exceed the current stock price of about $78. J.P. Morgan told it that it was unlikely to be competitive, “and accordingly Bidder 3 did not submit a written offer” (p. 25). It made no offer in the final-bid solicitation.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#38</t>
+          <t>#34</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>If Informal, the Buyer Group’s formal price path is $80.70 → $83.00. No count or round changes.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n"/>
+          <t>Dropped by target would put the exit decision on J.P. Morgan’s signal. Withdrew would treat the verbal statement as a declared exit. The revealed valuation (not above about $78) is the same either way.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>What was the outcome of the 12/12/2014 improved-bid deadline?</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Enforced.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Both bidders submitted on the evening of 12/12, the Buyer Group raising $82.50 to $83.00 within hours. The board reviewed these final bids on 12/13, and the agreement was signed on 12/14 (p. 26).</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>#35, #37</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Minor: Passed without action would apply only if the later $83.00 is read as further bargaining after the due date.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3910,8 +4044,8 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3946,7 +4080,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Argos Holdings Inc. (Parent; merger sub Argos Merger Sub Inc.), affiliated with funds advised by BC Partners and owned at closing by the Buyer Group: BC Partners funds, La Caisse de dépôt et placement du Québec, GIC Special Investments affiliates, StepStone Group affiliates and, after 12/12/2014, Longview Asset Management as rollover holder</t>
+          <t>Argos Holdings Inc. (Parent) and Argos Merger Sub Inc., affiliates of funds advised by BC Partners, Inc.; at closing owned by the Buyer Group: BC Partners funds, La Caisse de dépôt et placement du Québec, affiliates of GIC Special Investments Pte Ltd, affiliates of StepStone Group LP and Longview Asset Management, LLC</t>
         </is>
       </c>
     </row>
@@ -3958,7 +4092,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Financial (private-equity-led consortium; Longview rollover is support, not a group member)</t>
+          <t>Financial (private-equity-led consortium; Longview, an existing shareholder, rolls over part of its shares)</t>
         </is>
       </c>
     </row>
@@ -3970,7 +4104,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$83.00 per share in cash; Longview rolls 3,012,050 shares (about $250 million) into Parent instead of taking cash</t>
+          <t>$83.00 per share in cash; Longview contributes 3,012,050 shares (about $250 million) to Parent instead of receiving cash for them. Funded by about $6.2 billion committed debt, up to $1.83 billion cash equity and the rollover; total about $8.4 billion</t>
         </is>
       </c>
     </row>
@@ -3980,10 +4114,8 @@
           <t>Merger agreement signed</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>12/14/2014</t>
-        </is>
+      <c r="B6" s="4" t="n">
+        <v>41987</v>
       </c>
     </row>
     <row r="7">
@@ -3992,10 +4124,8 @@
           <t>Merger announced</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>12/14/2014</t>
-        </is>
+      <c r="B7" s="4" t="n">
+        <v>41987</v>
       </c>
     </row>
     <row r="8">
@@ -4040,10 +4170,8 @@
           <t>Number of processes</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B11" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -4054,7 +4182,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Undated, unspecified inquiries “from time to time” about the Company’s interest in a sale (p. 21). Q1 and spring 2014: target-initiated exploration of a merger with or acquisition of Industry Participant, a private competitor. It said it was not for sale and raised antitrust concerns; no agreement. This was the target acting as possible acquirer, not a sale process, so it has no rows.</t>
+          <t>Undated third-party inquiries about the Company’s interest in a sale, “from time to time” (p. 21). Spring 2014 talks initiated by PetSmart about a merger with or acquisition of Industry Participant, which said it was not for sale; this was not a sale of PetSmart (p. 21)</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4194,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Met (process 1): 15 parties. The filing counts agreements with 15 “potentially interested financial buyers”, i.e. parties. No post-signing additions, so the pre-signing subtotal is also 15. Longview’s confidentiality agreements (before 12/09 and with the Buyer Group on 12/12) are rollover-holder agreements and do not count.</t>
+          <t>Met (process 1): 15 parties</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4230,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>J.P. Morgan Securities LLC (primary; retained July 2014, engagement letter effective 08/21/2014; fairness opinion); an unnamed financial advisor attended the 06/18/2014 board meeting</t>
+          <t>J.P. Morgan Securities LLC (retained July 2014; engagement letter effective 08/21/2014); an unnamed financial advisor attended the 06/18/2014 board meeting</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4254,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>PetSmart’s first-quarter report missed expectations in May 2014. Activists JANA Partners and Longview then pushed for a sale, and on 08/13/2014 the board decided to explore one, announcing it on 08/19/2014. The board refused to admit Industry Participant, a strategic competitor, on antitrust and information grounds. Of 27 parties that approached J.P. Morgan, 15 financial buyers signed confidentiality and standstill agreements, and six submitted non-binding indications on 10/30/2014; four at $80 or above advanced to a final round, where two teamed up as Bidder 3. On 12/10 the Buyer Group bid $80.70 and Bidder 2 $80.35, while Bidder 3 would not exceed the roughly $78 share price. Asked to improve by 12/12, Bidder 2 gave a best-and-final $81.50, and the BC Partners-led Buyer Group, helped by a Longview rollover, went from $82.50 to $83.00 cash, signed and announced on 12/14/2014.</t>
+          <t>After weak first-quarter results and pressure from activist shareholders JANA Partners and Longview, PetSmart’s board decided on 08/13/2014 to explore a sale. It announced the review on 08/19/2014 but refused to admit the competitor Industry Participant, citing antitrust risk. J.P. Morgan was contacted by 27 parties; 15 financial buyers signed confidentiality agreements in early October, and six submitted non-binding indications on 10/30/2014. The board advanced the four at or above $80.00, two of which then joined as Bidder 3. At the 12/10 deadline the Buyer Group bid $80.70 and Bidder 2 $80.35, while Bidder 3 valued PetSmart no higher than its ~$78 stock price and did not bid. Asked to improve by 12/12, Bidder 2 offered $81.50 and the Buyer Group, now working with Longview on a rollover, $83.00 in cash, which was signed and announced on 12/14/2014.</t>
         </is>
       </c>
     </row>

--- a/extraction/petsmart.xlsx
+++ b/extraction/petsmart.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -60,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -72,9 +72,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -442,13 +439,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
@@ -456,13 +453,13 @@
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
@@ -592,10 +589,10 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Some stockholders and interested parties</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
+          <t>Some stockholders and interested parties (unnamed)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Activist</t>
@@ -609,15 +606,15 @@
       </c>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Count: unknown. After weak Q1 results (05/21/2014), stockholders and interested parties suggested strategic or financial alternatives, including a levered return of capital and a sale. Senders not named.</t>
+          <t>Count: unknown. After the 05/21/2014 earnings miss, stockholders and interested parties urged alternatives including a levered return of capital and a sale. Longview also met directors and management in May 2014 but advocated no specific transaction.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -625,13 +622,13 @@
           <t>“the Company received written or verbal communications from some stockholders and from interested parties suggesting that the Company engage in various strategic or financial alternatives” (p. 21)</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
       <c r="T2" s="4" t="n">
-        <v>41799</v>
+        <v>41800</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>41779</v>
+        <v>41780</v>
       </c>
       <c r="V2" s="4" t="n">
         <v>41820</v>
@@ -648,10 +645,10 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Unnamed financial advisor</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
+          <t>Wachtell, Lipton, Rosen &amp; Katz</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Adviser</t>
@@ -665,24 +662,24 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Target financial adviser, unnamed, attended the 06/18/2014 board review of alternatives. Board then authorized vetting and retention of a financial advisor and retained J.P. Morgan (#6); filing does not say whether this advisor continued.</t>
+          <t>Target legal adviser, first shown acting at the 06/18/2014 board meeting. The board then chose to explore capital-structure changes (return of capital), not a sale, and formed an ad hoc committee of independent directors (Josefowicz, Gangwal, Stemberg).</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>“the board reviewed, together with a financial advisor and with Wachtell, Lipton, Rosen &amp; Katz (“Wachtell Lipton”), its legal advisor” (p. 21)</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
+          <t>“together with a financial advisor and with Wachtell, Lipton, Rosen &amp; Katz (“Wachtell Lipton”), its legal advisor” (p. 21)</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
       <c r="T3" s="4" t="n">
         <v>41808</v>
       </c>
@@ -704,10 +701,10 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Wachtell, Lipton, Rosen &amp; Katz</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>Unnamed financial advisor</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Adviser</t>
@@ -721,24 +718,24 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Target legal adviser throughout. At this meeting the board chose to explore capital-structure changes (return of capital), not a sale, and formed the ad hoc committee (Josefowicz, Gangwal, Stemberg).</t>
+          <t>Target financial adviser at the 06/18/2014 board review of alternatives; not named. The filing does not say whether it is J.P. Morgan, which was retained only in July after interviews (see #6).</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>“the board reviewed, together with a financial advisor and with Wachtell, Lipton, Rosen &amp; Katz (“Wachtell Lipton”), its legal advisor” (p. 21)</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
+          <t>“At a meeting on June 18, 2014, the board reviewed, together with a financial advisor and with Wachtell” (p. 21)</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
       <c r="T4" s="4" t="n">
         <v>41808</v>
       </c>
@@ -763,7 +760,7 @@
           <t>JANA Partners</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Activist</t>
@@ -777,15 +774,15 @@
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Schedule 13D: 9.9% stake; intends to discuss strategic alternatives including a sale. Met the Company 07/10/2014 advocating a sale; further 13D amendments and public letters in July and August advocating a sale.</t>
+          <t>JANA filed a 13D disclosing a 9.9% stake and plans to discuss strategic alternatives including a sale; met the Company 07/10/2014 advocating a sale; further 13D amendments and public letters in July–August pressed for a sale.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -793,8 +790,8 @@
           <t>“JANA Partners filed a Schedule 13D with the SEC disclosing that JANA had acquired 9.9% of the Company’s outstanding common stock” (p. 22)</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2" t="n"/>
       <c r="T5" s="4" t="n">
         <v>41823</v>
       </c>
@@ -819,7 +816,7 @@
           <t>Longview Asset Management</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Activist</t>
@@ -833,24 +830,24 @@
       </c>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Public letter: board should consider a sale; Longview might roll part or all of its holdings into acquirer equity if needed. Met board in May 2014 without advocating a transaction; reiterated sale advocacy 07/10/2014.</t>
+          <t>Longview published a letter urging the board to consider a sale and offering to consider rolling part or all of its holdings into the acquirer if needed to complete a deal; reiterated its advocacy of a sale on 07/10/2014.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>“Longview made public a letter to the board in which Longview stated that the board should consider the a sale of the Company” (p. 22)</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
+          <t>“Longview would consider, depending on the parties and terms involved, rolling part or all of its holdings into equity of the acquiring entity rather than receive cash consideration” (p. 22)</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
       <c r="T6" s="4" t="n">
         <v>41827</v>
       </c>
@@ -875,7 +872,7 @@
           <t>J.P. Morgan Securities LLC</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Adviser</t>
@@ -889,15 +886,15 @@
       </c>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Target financial adviser, retained in July after interviews; engagement letter effective 08/21/2014 (Opinion section, p. 30). Rendered fairness opinion on $83.00 on 12/13/2014 (written 12/14/2014). Order against #4–#5 unknown.</t>
+          <t>Target financial adviser, retained in July after the board authorised a search on 06/18 and several advisers were interviewed. Fee up to about $39 million, mostly contingent (p. 36); JPM had received about $110 million from Buyer Group members over two years (p. 36).</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -905,8 +902,8 @@
           <t>“In July, after interviewing several potential financial advisors, the Company retained J.P. Morgan as financial advisor” (p. 22)</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="n"/>
+      <c r="S7" s="2" t="n"/>
       <c r="T7" s="4" t="n">
         <v>41836</v>
       </c>
@@ -949,26 +946,30 @@
       </c>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>First contact in the sale process, inbound to J.P. Morgan, no price. Privately held industry competitor with controlling stockholders. Spring 2014 talks were PetSmart-initiated; Industry Participant then said it was not for sale and raised antitrust concerns.</t>
+          <t>First contact in this process: a privately held industry rival, having heard J.P. Morgan was working with PetSmart, said it might revisit the spring 2014 talks on a combination if PetSmart pursued alternatives. No price. Earlier talks: Deal facts.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“Industry Participant might be interested in re-visiting the conversations that had taken place in the Spring concerning the feasibility of a possible combination” (p. 22)</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
+          <t>“Industry Participant might be interested in re-visiting the conversations that had taken place in the Spring concerning the feasibility of a possible combination of the two Companies” (p. 22)</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="n"/>
       <c r="T8" s="4" t="n">
         <v>41858</v>
       </c>
@@ -993,7 +994,7 @@
           <t>PetSmart</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Target sale decision</t>
@@ -1007,24 +1008,24 @@
       </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Board decided to explore alternatives including a sale; Profit Improvement Plan for sale or standalone; ad hoc committee to oversee. Planned J.P. Morgan outreach for late September/early October and a public announcement; weighed antitrust and information risks of inviting Industry Participant.</t>
+          <t>Board decided to explore strategic alternatives including a possible sale, alongside a standalone Profit Improvement Plan. Ad hoc committee to oversee. J.P. Morgan to contact financial and strategic parties in late September/early October. Public announcement planned. Board weighed excluding Industry Participant on antitrust grounds.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“determined to explore strategic alternatives (including a possible sale of the Company) for the Company to maximize value for stockholders” (p. 22)</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
+          <t>“determined to explore strategic alternatives (including a possible sale of the Company) for the Company to maximize value for stockholders including by commencing a process” (p. 22)</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="n"/>
+      <c r="S9" s="2" t="n"/>
       <c r="T9" s="4" t="n">
         <v>41864</v>
       </c>
@@ -1049,7 +1050,7 @@
           <t>PetSmart</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Sale process announced</t>
@@ -1063,15 +1064,15 @@
       </c>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Press release with Q2 earnings: exploring strategic alternatives including a possible sale. Board intended it to let uncontacted interested parties approach J.P. Morgan.</t>
+          <t>Press release with Q2 earnings announced the exploration of strategic alternatives including a possible sale.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1079,8 +1080,12 @@
           <t>“the Company issued a press release announcing that it determined to explore strategic alternatives for the Company to maximize value for stockholders, including a possible sale of the Company” (p. 23)</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="n"/>
       <c r="T10" s="4" t="n">
         <v>41870</v>
       </c>
@@ -1105,7 +1110,7 @@
           <t>PetSmart</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Round opened</t>
@@ -1119,20 +1124,24 @@
       </c>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Round 1 (indications of interest) opens with the public announcement (#9), the direct execution of the 08/13 decision and the first solicitation of buyers; inbound contacts followed (#12–#13). Planned outbound outreach is not separately reported.</t>
+          <t>Round 1 opening inferred: the 08/13 board decision made this announcement the public solicitation, so that parties J.P. Morgan had not contacted could approach it. No date is given for J.P. Morgan’s own outreach (planned late September/early October). Inbound contacts began mid-August.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“would ensure that interested parties not contacted would become aware of the process and could contact J.P. Morgan on their own initiative” (p. 22)</t>
+          <t>“which would ensure that interested parties not contacted would become aware of the process and could contact J.P. Morgan on their own initiative” (p. 22)</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1140,7 +1149,7 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="n"/>
       <c r="T11" s="4" t="n">
         <v>41870</v>
       </c>
@@ -1183,30 +1192,30 @@
       </c>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Target refuses admission: ad hoc committee had J.P. Morgan convey board concerns (call 08/22); on 08/27 Industry Participant said it would discuss a combination and was told it would not be invited, though a proposal would be considered. No contact since; board reaffirmed 10/03/2014.</t>
+          <t>Target refused admission on the ad hoc committee’s direction: antitrust risk, information leakage, delay. J.P. Morgan relayed concerns 08/22; on 08/27 Industry Participant said it was interested in discussing a combination. J.P. Morgan said it would not be invited but the board would consider any proposal. No contact since. Board reaffirmed 10/03/2014 (p. 23).</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>“The J.P. Morgan representative stated that Industry Participant would not be invited into the exploratory process” (p. 23)</t>
+          <t>“The J.P. Morgan representative stated that Industry Participant would not be invited into the exploratory process, but that if Industry Participant were to wish to submit a proposal” (p. 23)</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr"/>
+          <t>Q1; Q8</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="n"/>
       <c r="T12" s="4" t="n">
         <v>41878</v>
       </c>
@@ -1223,17 +1232,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>mid-August to end of October 2014</t>
+          <t>mid-August to by 10/03/2014</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24 financial parties</t>
+          <t>3 strategic parties (excluding Industry Participant)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1249,17 +1258,17 @@
       </c>
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Inbound: parties contacted J.P. Morgan. Includes potential lead buyers and large equity suppliers to lead buyers. Filing total 27 (with #13), excluding Industry Participant. Fifteen financial buyers signed NDAs (#14); overlap not stated but implied.</t>
+          <t>Inbound: they contacted J.P. Morgan (Reasons, p. 27: “contacted or were contacted by”). None signed a confidentiality agreement; all 15 signers were financial. The filing’s total of 27 is this row plus #13. Date to: the 10/03 board was updated on the 27.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1272,15 +1281,15 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="n"/>
       <c r="T13" s="4" t="n">
-        <v>41902</v>
+        <v>41888</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>41862</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>41943</v>
+        <v>41915</v>
       </c>
     </row>
     <row r="14">
@@ -1289,17 +1298,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>mid-August to end of October 2014</t>
+          <t>mid-August to by 10/03/2014</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3 strategic parties</t>
+          <t>24 financial parties</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1315,17 +1324,17 @@
       </c>
       <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Inbound: contacted J.P. Morgan; excludes Industry Participant. No strategic party signed an NDA (all 15 signers financial, #14), so none entered.</t>
+          <t>Inbound to J.P. Morgan. The 24 include possible lead buyers and large equity suppliers to lead buyers, so they are not all independent bidders (Q6). Date to: the 10/03 board was updated on communications with the 27.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1335,18 +1344,18 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr"/>
+          <t>Q1; Q6</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="n"/>
       <c r="T14" s="4" t="n">
-        <v>41902</v>
+        <v>41888</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>41862</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>41943</v>
+        <v>41915</v>
       </c>
     </row>
     <row r="15">
@@ -1381,30 +1390,30 @@
       </c>
       <c r="H15" s="3" t="n"/>
       <c r="I15" s="3" t="n"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Confidentiality and standstill agreements (standstills barred topping bids after signing, p. 28). All 15 did October diligence, got senior management presentations and detailed plan data incl. Profit Improvement Plan. Board told 10/03 approximately 15 parties interested.</t>
+          <t>Confidentiality and standstill agreements. All 15 got October diligence, senior-management presentations and detailed plan data, including the Profit Improvement Plan. Standstills bar topping bids after signing (p. 28). Includes Buyer Group, Bidder 2 and the other four IOI submitters. Whether the 15 are independent units is not stated (Q6).</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>“the Company entered into confidentiality and standstill agreements with 15 potentially interested financial buyers” (p. 23)</t>
+          <t>“In the first week of October 2014, the Company entered into confidentiality and standstill agreements with 15 potentially interested financial buyers” (p. 23)</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Q2; Q3</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr"/>
+          <t>Q1; Q6</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="n"/>
       <c r="T15" s="4" t="n">
         <v>41916</v>
       </c>
@@ -1421,7 +1430,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>October 2014</t>
+          <t>during October 2014</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1429,7 +1438,7 @@
           <t>PetSmart</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Deadline set</t>
@@ -1443,24 +1452,24 @@
       </c>
       <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="n"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Non-binding preliminary indications due 10/30/2014. Bidders told Longview would roll over up to 7.5 million shares on terms acceptable to it, if the bidder wished; asked to state interest in Longview, not a condition of participation.</t>
+          <t>Bidders told that non-binding preliminary indications of interest were due 10/30/2014. They were asked to state any interest in Longview participating (#16), which was not a condition of participation.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“the potential bidders were informed that non-binding preliminary indications of interest would be due on October 30, 2014” (p. 23)</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
+          <t>“During October, the potential bidders were informed that non-binding preliminary indications of interest would be due on October 30, 2014.” (p. 23)</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
       <c r="T16" s="4" t="n">
         <v>41927</v>
       </c>
@@ -1477,18 +1486,18 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>10/30/2014</t>
+          <t>during October 2014</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
+          <t>Longview Asset Management</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1499,36 +1508,32 @@
       </c>
       <c r="H17" s="3" t="n"/>
       <c r="I17" s="3" t="n"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Round 1 due date reached; six indications received (#17–#21). J.P. Morgan then called all 15 NDA signers, 10/30–11/02, about price rationales or non-submission.</t>
+          <t>Rollover offer disclosed to all bidders alike: Longview would roll up to 7.5 million shares into the buyer’s vehicle on terms and price acceptable to it, if the bidder wished.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>“On October 30, six of the potentially interested parties submitted indications of interest.” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr"/>
+          <t>“Longview had informed the Company that it would be willing to “roll-over” up to 7.5 million shares on terms and price acceptable to Longview” (p. 23)</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
       <c r="T17" s="4" t="n">
-        <v>41942</v>
+        <v>41928</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>41942</v>
+        <v>41913</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>41942</v>
+        <v>41943</v>
       </c>
     </row>
     <row r="18">
@@ -1542,17 +1547,13 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -1561,48 +1562,30 @@
       <c r="G18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Diligence still open (further diligence in November), no condition stated: Unclear. Non-binding preliminary indication; interest in Longview rollover, not a condition. Consortium composition at this date not stated.</t>
+          <t>Preliminary IOI due date reached; six parties submitted. Next step: J.P. Morgan calls 10/30–11/02, during which Bidder 2 raised its indication (#24), which the board considered on 11/03 (Q2).</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“including the Buyer Group, which indicated a range of $81.00 to $83.00 per share” (p. 24)</t>
+          <t>“On October 30, six of the potentially interested parties submitted indications of interest.” (p. 24)</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr"/>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="n"/>
       <c r="T18" s="4" t="n">
         <v>41942</v>
       </c>
@@ -1624,7 +1607,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Unnamed financial bidder 1</t>
+          <t>Buyer Group</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1644,10 +1627,10 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1667,24 +1650,24 @@
       <c r="M19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Diligence still open, no condition stated: Unclear. Non-binding preliminary indication. One of three initial indications reaching $80; advanced 11/03 (#24). Inferred to be a Bidder 3 member (#27).</t>
+          <t>Conditions Unclear: non-binding preliminary IOI; financing not reported; extensive diligence continued in November. BC Partners-led consortium; membership at this date not stated (Q6). Some interest in a Longview rollover, but its bid was not conditioned on it.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“another bidder, which suggested a range of $80.00 to $85.00 per share” (p. 24)</t>
+          <t>“including the Buyer Group, which indicated a range of $81.00 to $83.00 per share” (p. 24)</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr"/>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="n"/>
       <c r="T19" s="4" t="n">
         <v>41942</v>
       </c>
@@ -1706,7 +1689,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Unnamed financial bidder 2</t>
+          <t>Unnamed financial bidder 1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1725,8 +1708,12 @@
       <c r="G20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
+      <c r="H20" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>85</v>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -1745,24 +1732,24 @@
       <c r="M20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Diligence still open, no condition stated: Unclear. Third initial indication whose range reached at least $80.00; endpoints not disclosed, so price cells blank. Advanced 11/03 (#24); inferred to be a Bidder 3 member (#27).</t>
+          <t>Conditions Unclear: non-binding preliminary IOI; financing not reported; diligence continued. Among the three initial ranges reaching $80.00. Advanced on 11/03. Inferred to have joined Bidder 3 (#29, Q4).</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“Three bidders initially indicated price ranges that reached at least $80.00 per share” (p. 24)</t>
+          <t>“and another bidder, which suggested a range of $80.00 to $85.00 per share” (p. 24)</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr"/>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="n"/>
       <c r="T20" s="4" t="n">
         <v>41942</v>
       </c>
@@ -1784,7 +1771,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2</t>
+          <t>Unnamed financial bidder 2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1803,12 +1790,8 @@
       <c r="G21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>78</v>
-      </c>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -1827,20 +1810,24 @@
       <c r="M21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Diligence still open, no condition stated: Unclear. Non-binding preliminary indication at a point price of $78.00; revised by #23.</t>
+          <t>Conditions Unclear: non-binding preliminary IOI; diligence continued. The third bidder whose initial range “reached at least $80.00”. Endpoints not given, so price cells blank. Advanced on 11/03. Inferred to have joined Bidder 3 (#29, Q4).</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>“another bidder (which we refer to as “Bidder 2”), which had initially indicated a price of $78.00” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr"/>
+          <t>“Three bidders initially indicated price ranges that reached at least $80.00 per share” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="n"/>
       <c r="T21" s="4" t="n">
         <v>41942</v>
       </c>
@@ -1862,7 +1849,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2 other indication submitters</t>
+          <t>Bidder 2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1881,8 +1868,12 @@
       <c r="G22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
+      <c r="H22" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>78</v>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -1899,26 +1890,22 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Diligence still open, no condition stated: Unclear. 6 submitters − 4 named or described (#17–#20) = 2. Prices not disclosed; below $80.00, as they were not among the four at or above $80 (#24).</t>
+          <t>Conditions Unclear: non-binding preliminary IOI; diligence continued. Initial point indication of $78.00, raised within days (#24).</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>“On October 30, six of the potentially interested parties submitted indications of interest.” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr"/>
+          <t>“another bidder (which we refer to as “Bidder 2”), which had initially indicated a price of $78.00” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
       <c r="T22" s="4" t="n">
         <v>41942</v>
       </c>
@@ -1935,12 +1922,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>by 10/30/2014</t>
+          <t>10/30/2014</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9 NDA signers without an indication</t>
+          <t>2 other IOI submitters</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1950,7 +1937,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1961,38 +1948,48 @@
       </c>
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15 NDA signers (#14) − 6 submitters (#16) = 9. Filing confirms non-submitters and that J.P. Morgan heard their rationales, which are not disclosed. Not reported again.</t>
+          <t>Conditions Unclear: terms not reported. Count: 6 submitters − 4 described individually = 2. Prices not disclosed; below the $80.00 advancement threshold, since neither advanced (#25). The Reasons section says 5 “bidder groups” submitted (Q4).</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“including those that did not submit an indication of interest” (p. 24)</t>
+          <t>“On October 30, six of the potentially interested parties submitted indications of interest.” (p. 24)</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr"/>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="n"/>
       <c r="T23" s="4" t="n">
         <v>41942</v>
       </c>
-      <c r="U23" s="4" t="n"/>
+      <c r="U23" s="4" t="n">
+        <v>41942</v>
+      </c>
       <c r="V23" s="4" t="n">
         <v>41942</v>
       </c>
@@ -2003,12 +2000,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>10/30/2014 to 11/02/2014</t>
+          <t>by 10/30/2014</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2</t>
+          <t>9 NDA signers without an IOI</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2018,7 +2015,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -2027,56 +2024,46 @@
       <c r="G24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Diligence still open, no condition stated: Unclear. Revises #20 from $78.00 after J.P. Morgan calls; arrived after the 10/30 due date and was considered, qualifying Bidder 2 for the next round (#24).</t>
+          <t>Count: 15 NDA signers − 6 IOI submitters = 9. Assumes all six submitters were among the 15 signers. J.P. Morgan asked non-submitters for their reasons; the reasons are not reported. Some may have been equity partners who later joined bidding groups (Q6).</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>“As a result of its discussions with J.P. Morgan, another bidder (which we refer to as “Bidder 2”), which had initially indicated a price of $78.00, increased its indication” (p. 24)</t>
+          <t>“spoke by telephone with all of the potentially interested parties, including those that did not submit an indication of interest” (p. 24)</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr"/>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="n"/>
       <c r="T24" s="4" t="n">
-        <v>41943</v>
-      </c>
-      <c r="U24" s="4" t="n">
         <v>41942</v>
       </c>
+      <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n">
-        <v>41945</v>
+        <v>41942</v>
       </c>
     </row>
     <row r="25">
@@ -2085,58 +2072,80 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>11/03/2014</t>
+          <t>between 10/30/2014 and 11/02/2014</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
+          <t>Bidder 2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="n"/>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Board advanced the four bidders at or above $80.00 (Buyer Group, Bidder 2, Unnamed financial bidders 1–2) to a “final round”. All got further diligence and management presentations in November; form merger agreement circulated with comments due with final bids.</t>
+          <t>Conditions Unclear: still a non-binding indication; diligence continued. Revises #21 from $78.00 after J.P. Morgan’s post-deadline calls. It arrived after the 10/30 due date, and the board counted it on 11/03 (Q2).</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“allow the four bidders that had indicated a price or range at or above $80.00 per share to proceed to the final round of the sale process” (p. 24)</t>
+          <t>“which had initially indicated a price of $78.00, increased its indication to a range of $81.00 to $84.00 per share” (p. 24)</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q2</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr"/>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="n"/>
       <c r="T25" s="4" t="n">
-        <v>41946</v>
+        <v>41943</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>41946</v>
+        <v>41942</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>41946</v>
+        <v>41945</v>
       </c>
     </row>
     <row r="26">
@@ -2150,7 +2159,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2 other indication submitters</t>
+          <t>2 eliminated IOI submitters</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2171,21 +2180,21 @@
       </c>
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Would not improve earlier offer</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr"/>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Below the $80.00 cut. On notice, none showed interest or ability to stay in above its initial indication. Count: 6 submitters − 4 advancing = 2.</t>
+          <t>Board advanced only bidders at or above $80.00 (#26). When J.P. Morgan told them, neither eliminated party indicated any interest or ability to go above its initial indication. Count: 6 − 4 advanced = 2.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -2195,10 +2204,10 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>Q2; Q5</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr"/>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="n"/>
       <c r="T26" s="4" t="n">
         <v>41946</v>
       </c>
@@ -2215,7 +2224,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>by 12/03/2014</t>
+          <t>11/03/2014</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2223,10 +2232,10 @@
           <t>PetSmart</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -2237,36 +2246,36 @@
       </c>
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Final bids initially due Friday 12/05/2014, with completion targeted for 12/15 to leave time for further bidding rounds if needed, documentation and a possible Longview rollover. Day set not reported; after the 11/03 round opening.</t>
+          <t>Board admitted to the “final round” the four bidders at or above $80.00: Buyer Group, Bidder 2, and Unnamed financial bidders 1 and 2. November: further diligence and management presentations for all. A form merger agreement was circulated, with comments due with final bids. Each finalist showed some interest in a Longview rollover without conditioning on it.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>“had initially set Friday, December 5 as the date for submission of bids” (p. 24)</t>
+          <t>“The board determined to allow the four bidders that had indicated a price or range at or above $80.00 per share to proceed to the final round” (p. 24)</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr"/>
+          <t>Q1; Q4</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="n"/>
       <c r="T27" s="4" t="n">
-        <v>41961</v>
+        <v>41946</v>
       </c>
       <c r="U27" s="4" t="n">
         <v>41946</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>41976</v>
+        <v>41946</v>
       </c>
     </row>
     <row r="28">
@@ -2275,12 +2284,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>after 11/03/2014, by 12/10/2014</t>
+          <t>during November 2014</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Bidder 3 (Unnamed financial bidders 1 and 2)</t>
+          <t>Final-round bidders</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2290,7 +2299,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Bidding group changed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2301,42 +2310,36 @@
       </c>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2 independent finalists become 1 joint bidder, “Bidder 3”, with ad hoc committee approval: one wanted an equity partner; the other would otherwise drop out. Group change reported; identifying members as #18 and #19 is inferred.</t>
+          <t>Count: 3 or 4 units, depending on timing against #29. After Q3 earnings, J.P. Morgan gave all finalists updated FY2014 projections, at bidders’ request. FY2020–2024 extrapolations were never given to the Buyer Group (p. 37).</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“the ad hoc committee authorized these two bidders to work together. We refer to these two bidders together as “Bidder 3.”” (p. 24)</t>
+          <t>“representatives of J.P. Morgan provided the bidders with updates to the Company’s fiscal year 2014 financial projections” (p. 24)</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr"/>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="n"/>
       <c r="T28" s="4" t="n">
-        <v>41964</v>
+        <v>41959</v>
       </c>
       <c r="U28" s="4" t="n">
         <v>41946</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>41983</v>
+        <v>41973</v>
       </c>
     </row>
     <row r="29">
@@ -2345,7 +2348,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>after 11/03/2014, by 12/10/2014</t>
+          <t>between 11/03/2014 and 12/03/2014</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2353,10 +2356,10 @@
           <t>PetSmart</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2367,32 +2370,36 @@
       </c>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Gave updated projections to all finalists: after Q3 earnings, at bidders’ request, J.P. Morgan provided updated FY2014 projections. FY2020–2024 extrapolations were never given to the Buyer Group (Projections section, p. 37).</t>
+          <t>Board initially set Friday 12/05/2014 for final bids, targeting completion on Monday 12/15. This left time for further bidding rounds if needed and for a Longview rollover negotiation. Superseded before arrival by #30.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“representatives of J.P. Morgan provided the bidders with updates to the Company’s fiscal year 2014 financial projections” (p. 24)</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr"/>
+          <t>“had initially set Friday, December 5 as the date for submission of bids” (p. 24)</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="n"/>
       <c r="T29" s="4" t="n">
-        <v>41964</v>
+        <v>41961</v>
       </c>
       <c r="U29" s="4" t="n">
         <v>41946</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>41983</v>
+        <v>41976</v>
       </c>
     </row>
     <row r="30">
@@ -2401,18 +2408,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>12/04/2014 to 12/05/2014</t>
+          <t>between 11/03/2014 and 12/10/2014</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>Bidder 3 (Unnamed financial bidders 1 and 2)</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Deadline revised</t>
+          <t>Bidding group changed</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -2423,36 +2434,42 @@
       </c>
       <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Ad hoc committee moved final bids from 12/05 to the evening of 12/10/2014, keeping 12/15 completion to cut leak risk; asked for markups of the merger agreement and transaction documents and financing commitments in advance.</t>
+          <t>One finalist wanted an equity partner; the other would drop out unless allowed to partner. With ad hoc committee approval, 2 independent units became 1 joint bidder, Bidder 3. Identities inferred: only three finalist groups remain and Reasons counts 5 IOI groups (Q4).</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“set the evening of Wednesday, December 10 (five days, rather than 10 days prior to the anticipated December 15 completion date) as the deadline for submission of final bids” (p. 25)</t>
+          <t>“the ad hoc committee authorized these two bidders to work together. We refer to these two bidders together as “Bidder 3.”” (p. 24)</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr"/>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="n"/>
       <c r="T30" s="4" t="n">
-        <v>41977</v>
+        <v>41964</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>41977</v>
+        <v>41946</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>41978</v>
+        <v>41983</v>
       </c>
     </row>
     <row r="31">
@@ -2461,18 +2478,18 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>12/09/2014</t>
+          <t>12/04/2014–12/05/2014</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Longview Asset Management</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline revised</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2483,20 +2500,20 @@
       </c>
       <c r="H31" s="3" t="n"/>
       <c r="I31" s="3" t="n"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Rollover relationship: after signing a confidentiality agreement, Longview held introductory meetings with the Buyer Group and Bidder 2 (not reported for Bidder 3). Bidders barred from disclosing intended prices. Buyer Group and Bidder 2 had sent draft comments 12/06.</t>
+          <t>Ad hoc committee shortened the timetable to reduce leak risk. Final bids now due the evening of 12/10 instead of 12/05. Bidders asked to send merger agreement and document markups and financing commitments early if possible.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“J.P. Morgan arranged introductory meetings between Longview and the Buyer Group, and between Longview and Bidder 2” (p. 25)</t>
+          <t>“set the evening of Wednesday, December 10 (five days, rather than 10 days prior to the anticipated December 15 completion date) as the deadline for submission of final bids” (p. 25)</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -2504,15 +2521,15 @@
           <t>Q3</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="n"/>
       <c r="T31" s="4" t="n">
-        <v>41982</v>
+        <v>41977</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>41982</v>
+        <v>41977</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>41982</v>
+        <v>41978</v>
       </c>
     </row>
     <row r="32">
@@ -2521,18 +2538,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>12/10/2014</t>
+          <t>12/06/2014</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>Buyer Group; Bidder 2</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2543,36 +2564,34 @@
       </c>
       <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Round 2 final-bid due date reached: written bids from Buyer Group (#32) and Bidder 2 (#33); verbal indication only from Bidder 3 (#34).</t>
+          <t>Buyer Group and Bidder 2 sent comments on the draft merger agreement and documents; the Buyer Group also delivered financing commitment documents. Bidder 3 sent nothing. Wachtell returned revised drafts to both on 12/08.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“On December 10, PetSmart received final bid letters along with revised versions of the merger agreement and other transaction documents from the Buyer Group and from Bidder 2” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr"/>
+          <t>“the Buyer Group and Bidder 2 submitted their respective comments on the draft merger agreement and other transaction documents, and the Buyer Group provided its financing commitment documents” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="n"/>
+      <c r="S32" s="2" t="n"/>
       <c r="T32" s="4" t="n">
-        <v>41983</v>
+        <v>41979</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>41983</v>
+        <v>41979</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>41983</v>
+        <v>41979</v>
       </c>
     </row>
     <row r="33">
@@ -2581,12 +2600,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>12/10/2014</t>
+          <t>12/09/2014</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group</t>
+          <t>Buyer Group; Bidder 2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2596,7 +2615,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2605,52 +2624,36 @@
       <c r="G33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H33" s="3" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Financing commitment documents delivered 12/06, no diligence condition reported: Light. Final bid letter with revised merger agreement and transaction documents; less conditional and closer to Company positions than Bidder 2. Not dependent on Longview rollover.</t>
+          <t>Information access: after Longview signed a confidentiality agreement, J.P. Morgan held introductory Longview meetings with Buyer Group and Bidder 2 only. Bidder 3 was not reported included. Bidders could not disclose intended prices to Longview.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“The Buyer Group offered $80.70 per share, in cash, and Bidder 2 offered $80.35 per share, in cash.” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
+          <t>“J.P. Morgan arranged introductory meetings between Longview and the Buyer Group, and between Longview and Bidder 2” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="n"/>
       <c r="T33" s="4" t="n">
-        <v>41983</v>
+        <v>41982</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>41983</v>
+        <v>41982</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>41983</v>
+        <v>41982</v>
       </c>
     </row>
     <row r="34">
@@ -2664,17 +2667,13 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2683,44 +2682,30 @@
       <c r="G34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>80.34999999999999</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>80.34999999999999</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Financing commitment not reported until 12/12; documents more conditional than Buyer Group’s: Unclear. Final bid letter with revised merger agreement. Not dependent on Longview; partnering only after signing.</t>
+          <t>Final-bid due date reached. Written bids came from Buyer Group and Bidder 2; Bidder 3 gave only an oral valuation. Outcome: Extended, because improved bids were requested for 12/12 (#37, Q3).</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“The Buyer Group offered $80.70 per share, in cash, and Bidder 2 offered $80.35 per share, in cash.” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
+          <t>“PetSmart received final bid letters along with revised versions of the merger agreement and other transaction documents from the Buyer Group and from Bidder 2” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="n"/>
       <c r="T34" s="4" t="n">
         <v>41983</v>
       </c>
@@ -2742,7 +2727,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Bidder 3</t>
+          <t>Buyer Group</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2752,7 +2737,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -2761,36 +2746,44 @@
       <c r="G35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="H35" s="3" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>Value at or below market price</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Verbally said its valuation would not exceed the current stock price, about $78 (Ref: approximately $78 current price, 12/10/2014). J.P. Morgan said it was unlikely to be competitive; accordingly no written offer.</t>
+          <t>Committed financing (documents delivered 12/06); no diligence condition reported. Final bid letter with revised merger agreement. Terms were less conditional, more protective of the Company and closer to its positions than Bidder 2’s. Not dependent on a Longview rollover.</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>“Bidder 3 verbally communicated to J.P. Morgan that their valuation would not be above the current stock price of approximately $78 per share.” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr"/>
+          <t>“The Buyer Group offered $80.70 per share, in cash, and Bidder 2 offered $80.35 per share, in cash.” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="n"/>
       <c r="T35" s="4" t="n">
         <v>41983</v>
       </c>
@@ -2812,45 +2805,63 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>Bidder 2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Ad hoc committee: no assurance the board would approve either bid unless improved; bids close and not best offers. Buyer Group and Bidder 2 told to raise bids, due 12/12/2014. J.P. Morgan confirmed Longview’s rollover willingness on 12/11.</t>
+          <t>Conditions Unclear: financing commitments not reported until 12/12; its documents were more conditional than the Buyer Group’s, with specifics not given. Final bid letter with revised merger agreement. Not dependent on a rollover; any Longview partnering only after signing.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“instructed J.P. Morgan to inform each bidder that it would need to increase its bid, and to instruct the bidders to submit improved bids on December 12, 2014” (p. 25)</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>Q1; Q6; Q8</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr"/>
+          <t>“The Buyer Group offered $80.70 per share, in cash, and Bidder 2 offered $80.35 per share, in cash.” (p. 25)</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="n"/>
       <c r="T36" s="4" t="n">
         <v>41983</v>
       </c>
@@ -2867,12 +2878,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>12/12/2014</t>
+          <t>12/10/2014</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group</t>
+          <t>Bidder 3</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2882,49 +2893,53 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Value at or below market price</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Rollover support and information difference: committee let Buyer Group work with Longview; they signed a confidentiality agreement sharing bid price. Bidder 2 would accommodate Longview only after signing, with no price effect. Longview offered a voting agreement.</t>
+          <t>Bidder 3 said orally its valuation would not exceed the current price. J.P. Morgan said it was unlikely to be competitive, so it made no written offer. Ref: about $78 share price, 12/10/2014. Treated as a valuation statement, not a Bid (Q5).</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“later that day, Longview and the Buyer Group entered into a confidentiality agreement permitting the exchange of detailed information between them, including bid price” (p. 26)</t>
+          <t>“Bidder 3 verbally communicated to J.P. Morgan that their valuation would not be above the current stock price of approximately $78 per share.” (p. 25)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q3</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr"/>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="n"/>
       <c r="T37" s="4" t="n">
-        <v>41985</v>
+        <v>41983</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>41985</v>
+        <v>41983</v>
       </c>
       <c r="V37" s="4" t="n">
-        <v>41985</v>
+        <v>41983</v>
       </c>
     </row>
     <row r="38">
@@ -2933,7 +2948,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>12/12/2014</t>
+          <t>12/10/2014</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2941,50 +2956,50 @@
           <t>PetSmart</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Deadline revised</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" s="3" t="n"/>
       <c r="I38" s="3" t="n"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Round 3 due date reached; improved bids received that evening from Bidder 2 (#38) and Buyer Group (#39–#40).</t>
+          <t>Ad hoc committee, seeing close bids and neither as a best offer, said approval was not assured unless bids improved. J.P. Morgan told Buyer Group and Bidder 2 to increase and resubmit on 12/12. On 12/11 J.P. Morgan confirmed Longview was still willing to roll over shares.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“to instruct the bidders to submit improved bids on December 12, 2014” (p. 25)</t>
+          <t>“instructed J.P. Morgan to inform each bidder that it would need to increase its bid, and to instruct the bidders to submit improved bids on December 12, 2014” (p. 25)</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q8</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr"/>
+          <t>Q1; Q3</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="n"/>
       <c r="T38" s="4" t="n">
-        <v>41985</v>
+        <v>41983</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>41985</v>
+        <v>41983</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>41985</v>
+        <v>41983</v>
       </c>
     </row>
     <row r="39">
@@ -2998,7 +3013,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2</t>
+          <t>Buyer Group</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3008,49 +3023,33 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Financing commitment documents submitted, no diligence condition reported: Light. Evening offer with revised merger agreement draft; J.P. Morgan confirmed it was Bidder 2’s best and final. Revises #33.</t>
+          <t>Rollover relationship: the committee approved the Buyer Group’s request to work with Longview; they signed a confidentiality agreement sharing bid price. Bidder 2 said a rollover would not change its price and was accepted only after signing. Not a group change (E4).</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“During the evening of December 12, 2014, Bidder 2 submitted an offer of $81.50 per share, in cash.” (p. 26)</t>
+          <t>“Early in the day on December 12, 2014, the Buyer Group requested permission to work more closely with Longview in order to include a rollover” (p. 25)</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -3058,7 +3057,7 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="n"/>
       <c r="T39" s="4" t="n">
         <v>41985</v>
       </c>
@@ -3080,67 +3079,45 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Financing commitments delivered, no diligence condition reported: Light. Oral offer, stated as being raised within hours; formal by its standing 12/10 markup and revised drafts submitted that evening. Revises #32.</t>
+          <t>Improved-bid due date reached; both bidders submitted that evening. Outcome: Enforced, because the board acted on the bids in hand on 12/13 (#43, Q3).</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“The Buyer Group initially submitted an oral offer of $82.50 per share, in cash, but stated that it was working to increase the offer within the next few hours.” (p. 26)</t>
+          <t>“instruct the bidders to submit improved bids on December 12, 2014” (p. 25)</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr"/>
+          <t>Q1; Q3</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="n"/>
       <c r="T40" s="4" t="n">
         <v>41985</v>
       </c>
@@ -3162,7 +3139,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group</t>
+          <t>Bidder 2</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3179,13 +3156,13 @@
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>83</v>
+        <v>81.5</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>83</v>
+        <v>81.5</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3205,16 +3182,16 @@
       <c r="M41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Financing commitment documents submitted; drafts substantially executable with few exceptions: Light. Best and final; revises #39. Group said some members could not go higher and Longview’s $250 million rollover helped reach $83.00 (p. 27).</t>
+          <t>Committed financing: commitment documents sent with a revised merger agreement; no diligence condition reported. Confirmed to J.P. Morgan that evening as its best and final offer. Revises #35.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“Later in the evening, the Buyer Group submitted a best and final offer of $83.00 per share, in cash.” (p. 26)</t>
+          <t>“During the evening of December 12, 2014, Bidder 2 submitted an offer of $81.50 per share, in cash.” (p. 26)</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -3222,7 +3199,7 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="n"/>
       <c r="T41" s="4" t="n">
         <v>41985</v>
       </c>
@@ -3239,58 +3216,80 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/14/2014</t>
+          <t>12/12/2014</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Simpson Thacher and Bartlett LLP</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>Buyer Group</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="n"/>
-      <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Buyer-side legal adviser: named as copy recipient for Parent and Merger Sub in the merger agreement notices (Annex A, Section 8.7). Its role as counsel is inferred from that listing; earliest date shown is the agreement date.</t>
+          <t>Committed financing already delivered (12/06). Oral offer; said it was working to raise it within hours. Formal: it answered the final-round improvement request and rested on its own merger agreement markup (Q7). Revises #34.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“Simpson Thacher and Bartlett LLP” (p. A-46)</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr"/>
+          <t>“The Buyer Group initially submitted an oral offer of $82.50 per share, in cash, but stated that it was working to increase the offer within the next few hours.” (p. 26)</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q7</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="n"/>
       <c r="T42" s="4" t="n">
-        <v>41987</v>
+        <v>41985</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>41987</v>
+        <v>41985</v>
       </c>
       <c r="V42" s="4" t="n">
-        <v>41987</v>
+        <v>41985</v>
       </c>
     </row>
     <row r="43">
@@ -3299,12 +3298,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/14/2014</t>
+          <t>12/12/2014</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2</t>
+          <t>Buyer Group</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3314,37 +3313,49 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
       <c r="M43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Best and final $81.50 versus Buyer Group’s $83.00; board approved the Buyer Group transaction on 12/13/2014 and the agreement was signed 12/14.</t>
+          <t>Committed financing; documents “with few exceptions” in executable form. Open points remained, so Light rather than None. Best and final; members would not go higher. Longview’s $250 million rollover helped reach $83.00 (p. 27). Revises #41.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>“The board noted that Bidder 2 had informed the Company’s representatives that $81.50 per share was its best and final offer.” (p. 27)</t>
+          <t>“Later in the evening, the Buyer Group submitted a best and final offer of $83.00 per share, in cash.” (p. 26)</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -3352,15 +3363,15 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="n"/>
       <c r="T43" s="4" t="n">
-        <v>41987</v>
+        <v>41985</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>41987</v>
+        <v>41985</v>
       </c>
       <c r="V43" s="4" t="n">
-        <v>41987</v>
+        <v>41985</v>
       </c>
     </row>
     <row r="44">
@@ -3369,48 +3380,42 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>12/14/2014</t>
+          <t>12/13/2014</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Buyer Group (Argos Holdings Inc.)</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="n"/>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>$83.00 cash per share. Parent owned by BC Partners funds, CDPQ, GIC, StepStone affiliates and Longview (rollover 3,012,050 shares; voting agreement 7,424,591 shares). Board approved 12/13 with J.P. Morgan opinion. Committed debt and $1.83 billion equity; no go-shop.</t>
+          <t>Board chose the Buyer Group, approving the $83.00 merger unanimously subject to resolving remaining open points in the agreement. J.P. Morgan gave its fairness opinion orally, confirmed in writing 12/14. The board noted Bidder 2’s $81.50 was best and final.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>“On December 14, 2014, the parties executed the merger agreement, the voting agreement and related transaction agreements” (p. 26)</t>
+          <t>“the board unanimously determined that the merger agreement and the transactions contemplated thereby, including the merger, were advisable and in the best interests of PetSmart and its stockholders” (p. 26)</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -3418,15 +3423,15 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="n"/>
       <c r="T44" s="4" t="n">
-        <v>41987</v>
+        <v>41986</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>41987</v>
+        <v>41986</v>
       </c>
       <c r="V44" s="4" t="n">
-        <v>41987</v>
+        <v>41986</v>
       </c>
     </row>
     <row r="45">
@@ -3435,60 +3440,258 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>12/14/2014</t>
+          <t>by 12/14/2014</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>PetSmart</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
+      <c r="G45" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="n"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Press release announcing the transaction issued on signing day. No unsolicited proposal received through 02/02/2015 (p. 28).</t>
+          <t>Inferred acquirer legal adviser: named as the copy recipient for Parent notices in the merger agreement (Annex A). The filing gives no role or date beyond that.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>“issued a press release announcing the transaction” (p. 26)</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr"/>
-      <c r="S45" s="2" t="inlineStr"/>
+          <t>“Simpson Thacher and Bartlett LLP 425 Lexington Avenue New York, NY 10017” (p. A-46)</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="n"/>
       <c r="T45" s="4" t="n">
         <v>41987</v>
       </c>
-      <c r="U45" s="4" t="n">
-        <v>41987</v>
-      </c>
+      <c r="U45" s="4" t="n"/>
       <c r="V45" s="4" t="n">
         <v>41987</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>12/14/2014</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Buyer Group (Argos Holdings Inc.)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Merger agreement signed</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>$83.00 per share in cash. Parent: Argos Holdings (BC Partners-affiliated). Signed with a Longview voting agreement (7,424,591 shares, about 7.5%) and rollover of 3,012,050 shares. Financing: $1.83 billion equity, $6.2 billion debt committed. Fees: $255 million payable by the Company, $510 million reverse. No-shop; no go-shop.</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>“On December 14, 2014, the parties executed the merger agreement, the voting agreement and related transaction agreements and issued a press release announcing the transaction.” (p. 26)</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="n"/>
+      <c r="T46" s="4" t="n">
+        <v>41987</v>
+      </c>
+      <c r="U46" s="4" t="n">
+        <v>41987</v>
+      </c>
+      <c r="V46" s="4" t="n">
+        <v>41987</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>12/14/2014</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Bidder 2</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Not selected at signing</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="n"/>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Still live at signing. Its best and final $81.50 (#40) was below the Buyer Group’s $83.00.</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>“neither of which was willing to make a definitive offer at a price above $81.50, which was lower than the $83.00 price offered by the Buyer Group” (p. 27)</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="n"/>
+      <c r="T47" s="4" t="n">
+        <v>41987</v>
+      </c>
+      <c r="U47" s="4" t="n">
+        <v>41987</v>
+      </c>
+      <c r="V47" s="4" t="n">
+        <v>41987</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>12/14/2014</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>PetSmart</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Merger announced</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n"/>
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Press release announcing the transaction. As of 02/02/2015 no unsolicited proposal had been received (p. 28).</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>“On December 14, 2014, the parties executed the merger agreement, the voting agreement and related transaction agreements and issued a press release announcing the transaction.” (p. 26)</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="n"/>
+      <c r="S48" s="2" t="n"/>
+      <c r="T48" s="4" t="n">
+        <v>41987</v>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>41987</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>41987</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V45"/>
+  <autoFilter ref="A1:V48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3499,7 +3702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3511,7 +3714,7 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3573,17 +3776,17 @@
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="4" t="n">
         <v>41870</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Public announcement of the strategic-alternatives review, inviting parties to contact J.P. Morgan (#10); NDAs first week of October (#14)</t>
+          <t>Public announcement (08/19/2014) of the exploration of alternatives including a sale, designed by the 08/13 board decision to let parties contact J.P. Morgan (inferred opening, Q1).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>15 financial NDA signers, unnamed as a set; among them Buyer Group, Bidder 2, Unnamed financial bidders 1 and 2, two other indication submitters and nine non-submitters. 3 strategic contacts never signed; Industry Participant refused admission</t>
+          <t>15 financial buyers under confidentiality and standstill agreements (first week of October): Buyer Group, Bidder 2, Unnamed financial bidders 1 and 2, and 11 unnamed. Industry Participant (strategic) was refused admission; 3 strategic contacts never signed.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3603,12 +3806,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>6: Buyer Group ($81.00–$83.00), Unnamed financial bidder 1 ($80.00–$85.00), Unnamed financial bidder 2 (range reaching at least $80), Bidder 2 ($78.00, raised to $81.00–$84.00 after the deadline), 2 others (undisclosed, below $80)</t>
+          <t>6: Buyer Group ($81–$83), Unnamed financial bidder 1 ($80–$85), Unnamed financial bidder 2 (range reaching at least $80), Bidder 2 ($78, then $81–$84 after the due date), 2 unnamed (below $80). The Reasons section counts 5 groups (Q4).</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Four advanced (at or above $80.00); two dropped by target; nine did not submit</t>
+          <t>four advanced, two dropped, nine did not submit</t>
         </is>
       </c>
     </row>
@@ -3619,27 +3822,27 @@
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="4" t="n">
         <v>41946</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Board selects the four bidders at or above $80.00 for the “final round” (#24)</t>
+          <t>Board selected the bidders at or above $80.00 for the announced “final round”; a form merger agreement was later circulated.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>4 financial: Buyer Group, Bidder 2, Unnamed financial bidders 1 and 2 (the last two joined as Bidder 3 in November, leaving 3 units)</t>
+          <t>4 financial: Buyer Group, Bidder 2, Unnamed financial bidder 1, Unnamed financial bidder 2. The last two combined as Bidder 3 during the round (inferred, Q4).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2014 (superseded before arrival) → 12/10/2014</t>
+          <t>12/05/2014 (superseded before arrival) → 12/10/2014 → 12/12/2014</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Enforced</t>
+          <t>Extended; Enforced</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -3649,63 +3852,17 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2 written: Buyer Group $80.70, Bidder 2 $80.35 (both cash, with merger agreement markups); Bidder 3 gave only a verbal valuation not above ~$78</t>
+          <t>2: Buyer Group ($80.70; then $82.50 and $83.00 on 12/12) and Bidder 2 ($80.35; then $81.50 best and final). Bidder 3 gave only an oral valuation at or below the ~$78 share price.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Two asked to improve (round 3); Bidder 3 did not submit</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>41983</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Ad hoc committee requires improved bids from Buyer Group and Bidder 2 by 12/12 (#35)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2 financial: Buyer Group, Bidder 2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12/12/2014</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Enforced</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Inferred final</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2: Bidder 2 $81.50 (best and final); Buyer Group $82.50 oral, then $83.00 best and final</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Signing with Buyer Group at $83.00 on 12/14/2014; Bidder 2 not selected</t>
+          <t>signing with Buyer Group at $83.00; Bidder 2 not selected; Bidder 3 did not submit</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
+  <autoFilter ref="A1:J3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3716,12 +3873,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -3773,30 +3930,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Is this one process with round 1 opening at the 08/19/2014 announcement, round 2 at the 11/03 final-round selection and round 3 at the 12/10 request for improved bids?</t>
+          <t>Process and round map: one process with two rounds (round 1 opened 08/19/2014, round 2 opened 11/03/2014), plus round 0 before the announcement and post after signing. Is this map right?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yes: one process; round 0 holds #1–#8; three rounds as mapped.</t>
+          <t>Keep one process and two rounds. Round 1 opens with the 08/19 announcement, which the 08/13 decision designed as the solicitation. Round 2 is the announced “final round” from 11/03; the 12/10 request to improve continues it.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The 08/19 announcement carried out the 08/13 decision and invited inbound contact (pp. 22–23); on 11/03 four were sent to the “final round” (p. 24); on 12/10 two selected bidders had to improve by 12/12 (p. 25). Gaps of two months or more without acquirer contact: none (longest about five weeks, 06/30/2014 to 08/07/2014). E5: (a) nothing to test, (b) no break, (c) no fresh start after 08/13; one process.</t>
+          <t>Alternatives: (i) round 1 opens at the first-week-of-October NDAs (p. 23), putting #9 and #11–#13 in round 0; (ii) the 12/10 request (p. 25) opens round 3, moving #37–#46. Gaps: none of about two months or more with no acquirer contact from 08/07 to signing. E5: (a) not met (activity continuous); (b) not met (no break reported or of about three months); (c) met only by the 08/13 decision, which starts process 1. The spring 2014 Industry Participant talks were about PetSmart combining with or buying a rival, and are undated beyond “Spring”, so they get no process.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#10–#13, #24, #35–#40, #42–#43</t>
+          <t>#9, #10, #11, #12, #13, #14, #26, #37, #38, #39, #40, #41, #42, #43, #44, #45, #46</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Alternative 1: round 1 opens with the early-October NDAs, moving #11–#13 to round 0. Alternative 2: the 12/10 request is bargaining within round 2, deleting #35, moving #36–#43 to round 2 and making the 12/10 outcome Extended.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Under (i), Industry Participant’s refusal and the 27 contacts leave round 1, which then starts with 15 entrants and no earlier contacts. Under (ii), round 2 stays Announced as final but its 12/10 outcome becomes Enforced, and a round 3 (Announced as final) holds the 12/12 bids, selection and signing.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3806,30 +3963,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Who formed Bidder 3, and were there six first-round indications or five?</t>
+          <t>Round 1 deadline outcome: the 10/30/2014 IOI due date. Enforced or Late bids accepted?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Bidder 3 = the other two finalists at or above $80 (Unnamed financial bidders 1 and 2); six indications, i.e. five bidder groups once Bidder 3 is counted as one.</t>
+          <t>Late bids accepted. Bidder 2 raised its indication from $78.00 to $81.00–$84.00 after the due date (10/30–11/02 calls), and the board counted it among the four at or above $80.00 on 11/03.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The background reports six indications and four finalists (p. 24). One Bidder 3 member was “invited into the final round”; the other would “drop out of the process” if it could not pair up, implying it was still in (p. 24). Only three finalists acted on 12/10, and Reasons cites indications “from 5 bidder groups” and “two other bidding groups” (p. 27).</t>
+          <t>p. 24: “As a result of its discussions with J.P. Morgan … increased its indication”; the board allowed “the four bidders that had indicated a price or range at or above $80.00”.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#14, #18–#19, #21–#22, #24–#25, #27</t>
+          <t>#17, #24</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>If the partner had been eliminated on 11/03, a fourth finalist left without a reported exit (add an inferred exit by 12/10), #25 includes the partner and a Re-entered row is needed. If only five indications, #21 becomes Count 1 and #22 Count 10.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>If the revision is seen as a clarification of a timely bid, the outcome is Enforced. Either way the Bid row stands, and Bidder 2’s admission to round 2 depends on its late revision.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3839,30 +3996,30 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Were Buyer Group members separate NDA signers who later combined, and is Longview’s 12/12 link a bidding-group change?</t>
+          <t>Round 2 deadline outcomes: 12/05 → 12/10 → 12/12. Is 12/05 superseded, and what happened at 12/10 and 12/12?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Treat the Buyer Group as one unit throughout, and Longview as rollover support (#36), not a group change.</t>
+          <t>Mark 12/05 “superseded before arrival”: the committee changed it on 12/04–12/05 and no bids were expected that day. Mark 12/10 Extended (improved bids requested for 12/12 in the same round) and 12/12 Enforced (board acted on 12/13).</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The filing names the Buyer Group from its 10/30 indication and never reports when it formed (p. 24); the 24 financial contacts included “large suppliers of equity capital to lead buyers” (p. 23). Longview is a shareholder rolling over shares, which E4 does not treat as a group; the definition adds Longview only after 12/12/2014 (p. 1).</t>
+          <t>p. 24–25: “had initially set Friday, December 5”, revised “on December 4 and December 5”; p. 25: “submit improved bids on December 12”; p. 26: the 12/13 board reviewed “the final bids”.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#14, #17, #30, #36</t>
+          <t>#28, #30, #33, #37, #39</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>If members signed separately, several of the 15 signers were Buyer Group members, round 1 had fewer independent units, and a Bidding group changed row before 10/30 would be needed.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>If the 12/05 change came after that date had passed, 12/05 needs a Deadline row with outcome Extended. If 12/10 opens a new round (Q1 alternative ii), the 12/10 outcome becomes Enforced.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3872,30 +4029,30 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>What was the outcome of the 10/30/2014 indication deadline?</t>
+          <t>Who formed Bidder 3, and why does the Reasons section count 5 IOI “bidder groups” when the Background counts six submitters?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Late bids accepted.</t>
+          <t>Treat Bidder 3 as Unnamed financial bidders 1 and 2, both admitted to round 2. That leaves three finalist groups, matching the December bidders, and makes the six IOIs five groups after combination.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bidder 2 raised its indication from $78.00 to $81.00–$84.00 between 10/30 and 11/02 after J.P. Morgan calls, and the board admitted it on that basis on 11/03 (p. 24). Other bidders’ indications are reported only as submitted on 10/30.</t>
+          <t>p. 24: one partner “had been invited into the final round”, the other “would drop out of the process” unless allowed to partner. p. 27: “first round indications of interest from 5 bidder groups” and “two other bidding groups”.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#16, #23</t>
+          <t>#19, #20, #22, #26, #29, #27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>If the revision is read as bargaining over an on-time bid, the outcome is Enforced (board acted on bids in hand on 11/03). Participation is unaffected.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>If the second partner was an eliminated or non-submitting party, one finalist (1 or 2) disappears silently. It would need an inferred Did not submit by 12/10, and the 2 eliminated or 9 non-submitters counts would fall by one.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3905,30 +4062,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Which exit reason fits the two indication submitters cut on 11/03?</t>
+          <t>Is Bidder 3’s 12/10 oral statement (valuation not above the ~$78 share price) a Bid, and which exit label fits?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Would not improve earlier offer.</t>
+          <t>Record no Bid: it is a valuation cap with no offer. Record Did not submit on 12/10, Exit reason Value at or below market price.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>They fell below the board’s $80.00 cut, and when notified none indicated any interest or ability to remain in the process above its initial indication (p. 24). That reveals a ceiling at their own bids.</t>
+          <t>p. 25: “their valuation would not be above the current stock price of approximately $78”; J.P. Morgan said it “was unlikely to be competitive and accordingly Bidder 3 did not submit a written offer.”</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#25</t>
+          <t>#36</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Lower offer than rivals would stress the cut against the four finalists and lose the fact that they would not raise.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+          <t>As a Bid, it gets an Informal row with Price high blank (the $78 is approximate) before the exit. If J.P. Morgan’s remark is read as exclusion, the label becomes Dropped by target.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3938,30 +4095,30 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>What happened to round 2’s due dates of 12/05 and 12/10/2014?</t>
+          <t>Are the 15 NDA signers independent bidder units? The Buyer Group’s composition at the time of its IOI is also not stated.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12/05 superseded before arrival (no outcome); 12/10 Enforced.</t>
+          <t>Keep Count 15 and 9 non-submitters, with the caveat in the Notes.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>On 12/04–12/05 the committee reset final bids to the evening of 12/10 (pp. 24–25); no bids are reported on 12/05. On 12/10 the committee acted on the bids in hand, requiring improved bids from two of the three bidders; Bidder 3 was not asked (p. 25).</t>
+          <t>p. 23: the 24 financial contacts included “large suppliers of equity capital to lead buyers”. Annex A §5.2: confidentiality agreements with “certain of the Equity Investors” (plural). p. 16: BC Partners, Caisse, GIC and StepStone make up the Buyer Group. None of this says who signed which of the 15.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#26, #29, #31, #35</t>
+          <t>#13, #14, #18, #23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>If 12/05 is treated as reached before the change, add a Deadline row with outcome Extended. If round 3 merges into round 2 (Q1), the 12/10 outcome becomes Extended.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
+          <t>If several Buyer Group members signed separately, the 15 overstate independent units. Some of the 9 “Did not submit” would instead be Bidding group changed into the Buyer Group, reducing live competition in round 1. The auction screen stays Met in any case.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3971,30 +4128,30 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Did Bidder 3 withdraw, fail to submit, or get dropped on 12/10?</t>
+          <t>Is the Buyer Group’s oral $82.50 on 12/12 Formal?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Did not submit; Value at or below market price.</t>
+          <t>Formal. It answered the final-round request for improved bids and was backed by the group’s own merger agreement markup and committed financing.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Bidder 3 said its valuation would not exceed the current stock price of about $78. J.P. Morgan told it that it was unlikely to be competitive, “and accordingly Bidder 3 did not submit a written offer” (p. 25). It made no offer in the final-bid solicitation.</t>
+          <t>p. 26: “initially submitted an oral offer of $82.50 … working to increase the offer within the next few hours”; p. 25: final bid letters with revised merger agreements on 12/10.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#34</t>
+          <t>#41</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target would put the exit decision on J.P. Morgan’s signal. Withdrew would treat the verbal statement as a declared exit. The revealed valuation (not above about $78) is the same either way.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>As Informal, the Buyer Group’s price path would show a formal-to-informal step within the final round. That affects how the model reads intra-round revisions.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -4004,33 +4161,66 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>What was the outcome of the 12/12/2014 improved-bid deadline?</t>
+          <t>Industry Participant: 08/07 Bidder interest in round 0, then the 08/27 refusal of admission. Should it be treated as a participant who exited?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Enforced.</t>
+          <t>No. It never signed an NDA, bid or was admitted, so it gets no entry or exit; the refusal is an Other material event. Its spring 2014 talks go to Deal facts, because PetSmart was then exploring a combination or acquisition as buyer.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Both bidders submitted on the evening of 12/12, the Buyer Group raising $82.50 to $83.00 within hours. The board reviewed these final bids on 12/13, and the agreement was signed on 12/14 (p. 26).</t>
+          <t>p. 21: “merger with or acquisition of another participant in PetSmart’s industry”; p. 23: “Industry Participant would not be invited into the exploratory process”.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>#35, #37</t>
+          <t>#7, #11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Minor: Passed without action would apply only if the later $83.00 is read as further bargaining after the due date.</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
+          <t>Treated as an entrant, it would add a strategic bidder to round 1 with a Dropped by target exit on 08/27. That changes the competition count and the strategic/financial mix.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Exit reason for the two IOI submitters eliminated on 11/03: Lower offer than rivals, or Would not improve earlier offer?</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Lower offer than rivals. The target cut them at its $80.00 threshold, and their later statement that they would not go higher was not a response to a request to improve.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>p. 24: the board advanced bidders “at or above $80.00”; the eliminated parties then showed no “interest or ability to remain … above their respective initial indications”.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>#25</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Would not improve earlier offer signals a firm valuation ceiling near the initial indication rather than a price below rivals.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4068,7 +4258,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>PetSmart, Inc.</t>
+          <t>PetSmart, Inc. (NASDAQ: PETM)</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4270,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Argos Holdings Inc. (Parent) and Argos Merger Sub Inc., affiliates of funds advised by BC Partners, Inc.; at closing owned by the Buyer Group: BC Partners funds, La Caisse de dépôt et placement du Québec, affiliates of GIC Special Investments Pte Ltd, affiliates of StepStone Group LP and Longview Asset Management, LLC</t>
+          <t>Argos Holdings Inc. (Parent) and Argos Merger Sub Inc., BC Partners-affiliated. At closing Parent is owned by the Buyer Group: funds advised by BC Partners, La Caisse de dépôt et placement du Québec, GIC Special Investments affiliates, StepStone Group affiliates and (after 12/12/2014) Longview Asset Management.</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4282,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Financial (private-equity-led consortium; Longview, an existing shareholder, rolls over part of its shares)</t>
+          <t>Financial (private-equity-led consortium with institutional co-investors and a rolling shareholder)</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4294,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$83.00 per share in cash; Longview contributes 3,012,050 shares (about $250 million) to Parent instead of receiving cash for them. Funded by about $6.2 billion committed debt, up to $1.83 billion cash equity and the rollover; total about $8.4 billion</t>
+          <t>$83.00 per share in cash. Longview contributes 3,012,050 shares (about $250 million) to Parent instead of cash and receives $83.00 cash on its other shares.</t>
         </is>
       </c>
     </row>
@@ -4114,8 +4304,10 @@
           <t>Merger agreement signed</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>41987</v>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>12/14/2014</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4124,8 +4316,10 @@
           <t>Merger announced</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>41987</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>12/14/2014</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4170,8 +4364,10 @@
           <t>Number of processes</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>1</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -4182,7 +4378,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Undated third-party inquiries about the Company’s interest in a sale, “from time to time” (p. 21). Spring 2014 talks initiated by PetSmart about a merger with or acquisition of Industry Participant, which said it was not for sale; this was not a sale of PetSmart (p. 21)</t>
+          <t>Undated: PetSmart “from time to time” received inquiries about its interest in a sale (p. 21). Q1–spring 2014: the board considered merging with or acquiring Industry Participant, a privately held rival. In March 2014 it authorized contact, and the CEOs spoke in spring 2014 and over the next two months. Industry Participant said it was not for sale and raised antitrust concerns (p. 21). PetSmart was the potential buyer, so this is not a sale process.</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4426,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>J.P. Morgan Securities LLC (retained July 2014; engagement letter effective 08/21/2014); an unnamed financial advisor attended the 06/18/2014 board meeting</t>
+          <t>J.P. Morgan Securities LLC (retained July 2014); an unnamed financial advisor attended the 06/18/2014 board meeting</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4450,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>After weak first-quarter results and pressure from activist shareholders JANA Partners and Longview, PetSmart’s board decided on 08/13/2014 to explore a sale. It announced the review on 08/19/2014 but refused to admit the competitor Industry Participant, citing antitrust risk. J.P. Morgan was contacted by 27 parties; 15 financial buyers signed confidentiality agreements in early October, and six submitted non-binding indications on 10/30/2014. The board advanced the four at or above $80.00, two of which then joined as Bidder 3. At the 12/10 deadline the Buyer Group bid $80.70 and Bidder 2 $80.35, while Bidder 3 valued PetSmart no higher than its ~$78 stock price and did not bid. Asked to improve by 12/12, Bidder 2 offered $81.50 and the Buyer Group, now working with Longview on a rollover, $83.00 in cash, which was signed and announced on 12/14/2014.</t>
+          <t>After a weak first quarter, activists JANA Partners (9.9%) and Longview pressed PetSmart to sell in mid-2014. On 08/13/2014 the board decided to explore a sale and announced it on 08/19, refusing to admit a strategic rival, Industry Participant, on antitrust grounds. Of 27 parties that contacted J.P. Morgan, 15 financial buyers signed confidentiality and standstill agreements, and six submitted preliminary indications on 10/30. On 11/03 the board sent the four at or above $80 to a final round, where two of them combined as Bidder 3. At the 12/10 final-bid deadline the Buyer Group bid $80.70 and Bidder 2 $80.35, while Bidder 3 valued the company no higher than the market price. After a request to improve, Bidder 2 bid $81.50 and the BC Partners-led Buyer Group, now working with Longview on a rollover, bid $83.00 in cash, and the merger agreement was signed on 12/14/2014.</t>
         </is>
       </c>
     </row>
